--- a/public/downloads/KHLOHC.xlsx
+++ b/public/downloads/KHLOHC.xlsx
@@ -8,35 +8,37 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="Allegro-OAM-L" sheetId="3" r:id="rId3"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="4" r:id="rId4"/>
-    <sheet name="CHGNetv0.3.0" sheetId="5" r:id="rId5"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="6" r:id="rId6"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="7" r:id="rId7"/>
-    <sheet name="eSEN-30M-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="GRACE-2L-OAM" sheetId="9" r:id="rId9"/>
-    <sheet name="MACE-MH-1-OC20" sheetId="10" r:id="rId10"/>
-    <sheet name="MACE-MH-1-OMAT" sheetId="11" r:id="rId11"/>
-    <sheet name="MACE-MPA-0" sheetId="12" r:id="rId12"/>
-    <sheet name="MATLANTISv8" sheetId="13" r:id="rId13"/>
-    <sheet name="MatterSim_v1_5M" sheetId="14" r:id="rId14"/>
-    <sheet name="NequIP-OAM-L" sheetId="15" r:id="rId15"/>
-    <sheet name="NequIP-OAM-XL" sheetId="16" r:id="rId16"/>
-    <sheet name="Nequix-MP-1" sheetId="17" r:id="rId17"/>
-    <sheet name="ORB-v3" sheetId="18" r:id="rId18"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="19" r:id="rId19"/>
-    <sheet name="SevenNet-Omni" sheetId="20" r:id="rId20"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="21" r:id="rId21"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="22" r:id="rId22"/>
-    <sheet name="UMA-s-1p2_oc20" sheetId="23" r:id="rId23"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="Allegro-OAM-L" sheetId="5" r:id="rId5"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="6" r:id="rId6"/>
+    <sheet name="CHGNetv0.3.0" sheetId="7" r:id="rId7"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="8" r:id="rId8"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="9" r:id="rId9"/>
+    <sheet name="eSEN-30M-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="GRACE-2L-OAM" sheetId="11" r:id="rId11"/>
+    <sheet name="MACE-MH-1-OC20" sheetId="12" r:id="rId12"/>
+    <sheet name="MACE-MH-1-OMAT" sheetId="13" r:id="rId13"/>
+    <sheet name="MACE-MPA-0" sheetId="14" r:id="rId14"/>
+    <sheet name="MATLANTISv8" sheetId="15" r:id="rId15"/>
+    <sheet name="MatterSim_v1_5M" sheetId="16" r:id="rId16"/>
+    <sheet name="NequIP-OAM-L" sheetId="17" r:id="rId17"/>
+    <sheet name="NequIP-OAM-XL" sheetId="18" r:id="rId18"/>
+    <sheet name="Nequix-MP-1" sheetId="19" r:id="rId19"/>
+    <sheet name="ORB-v3" sheetId="20" r:id="rId20"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="21" r:id="rId21"/>
+    <sheet name="SevenNet-Omni" sheetId="22" r:id="rId22"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="23" r:id="rId23"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="24" r:id="rId24"/>
+    <sheet name="UMA-s-1p2_oc20" sheetId="25" r:id="rId25"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="61">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -68,10 +70,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -189,6 +191,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>Tol</t>
@@ -683,10 +706,10 @@
         <v>694</v>
       </c>
       <c r="N3" s="5">
-        <v>1913.901945829391</v>
+        <v>1913901.945829391</v>
       </c>
       <c r="O3" s="4">
-        <v>0.04193291148129774</v>
+        <v>41.93291148129774</v>
       </c>
       <c r="P3" s="5">
         <v>45642</v>
@@ -733,10 +756,10 @@
         <v>694</v>
       </c>
       <c r="N4" s="5">
-        <v>2322.240045785904</v>
+        <v>2322240.045785904</v>
       </c>
       <c r="O4" s="4">
-        <v>0.04267176357997655</v>
+        <v>42.67176357997656</v>
       </c>
       <c r="P4" s="5">
         <v>54421</v>
@@ -783,10 +806,10 @@
         <v>694</v>
       </c>
       <c r="N5" s="5">
-        <v>7262.275715112686</v>
+        <v>7262275.715112686</v>
       </c>
       <c r="O5" s="4">
-        <v>0.09190776307772613</v>
+        <v>91.90776307772613</v>
       </c>
       <c r="P5" s="5">
         <v>79017</v>
@@ -833,10 +856,10 @@
         <v>691</v>
       </c>
       <c r="N6" s="5">
-        <v>5195.254918575287</v>
+        <v>5195254.918575287</v>
       </c>
       <c r="O6" s="4">
-        <v>0.1467295991915522</v>
+        <v>146.7295991915522</v>
       </c>
       <c r="P6" s="5">
         <v>35407</v>
@@ -883,10 +906,10 @@
         <v>691</v>
       </c>
       <c r="N7" s="5">
-        <v>7333.776261329651</v>
+        <v>7333776.261329651</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1004778290061468</v>
+        <v>100.4778290061468</v>
       </c>
       <c r="P7" s="5">
         <v>72989</v>
@@ -933,10 +956,10 @@
         <v>694</v>
       </c>
       <c r="N8" s="5">
-        <v>6903.975885152817</v>
+        <v>6903975.885152817</v>
       </c>
       <c r="O8" s="4">
-        <v>0.2698974153695394</v>
+        <v>269.8974153695394</v>
       </c>
       <c r="P8" s="5">
         <v>25580</v>
@@ -983,10 +1006,10 @@
         <v>691</v>
       </c>
       <c r="N9" s="5">
-        <v>1410.215593099594</v>
+        <v>1410215.593099594</v>
       </c>
       <c r="O9" s="4">
-        <v>0.02647248208405313</v>
+        <v>26.47248208405313</v>
       </c>
       <c r="P9" s="5">
         <v>53271</v>
@@ -1033,10 +1056,10 @@
         <v>694</v>
       </c>
       <c r="N10" s="5">
-        <v>7690.494214773178</v>
+        <v>7690494.214773178</v>
       </c>
       <c r="O10" s="4">
-        <v>0.1236731991311781</v>
+        <v>123.6731991311781</v>
       </c>
       <c r="P10" s="5">
         <v>62184</v>
@@ -1083,10 +1106,10 @@
         <v>694</v>
       </c>
       <c r="N11" s="5">
-        <v>4325.875496149063</v>
+        <v>4325875.496149063</v>
       </c>
       <c r="O11" s="4">
-        <v>0.1242425037667029</v>
+        <v>124.2425037667029</v>
       </c>
       <c r="P11" s="5">
         <v>34818</v>
@@ -1133,10 +1156,10 @@
         <v>694</v>
       </c>
       <c r="N12" s="5">
-        <v>9791.068883657455</v>
+        <v>9791068.883657455</v>
       </c>
       <c r="O12" s="4">
-        <v>0.1562845198432131</v>
+        <v>156.2845198432131</v>
       </c>
       <c r="P12" s="5">
         <v>62649</v>
@@ -1183,10 +1206,10 @@
         <v>694</v>
       </c>
       <c r="N13" s="5">
-        <v>2954.475812911987</v>
+        <v>2954475.812911987</v>
       </c>
       <c r="O13" s="4">
-        <v>0.09435903717262263</v>
+        <v>94.35903717262264</v>
       </c>
       <c r="P13" s="5">
         <v>31311</v>
@@ -1233,10 +1256,10 @@
         <v>694</v>
       </c>
       <c r="N14" s="5">
-        <v>4529.314520359039</v>
+        <v>4529314.520359039</v>
       </c>
       <c r="O14" s="4">
-        <v>0.05414148870218917</v>
+        <v>54.14148870218917</v>
       </c>
       <c r="P14" s="5">
         <v>83657</v>
@@ -1283,10 +1306,10 @@
         <v>694</v>
       </c>
       <c r="N15" s="5">
-        <v>584.4921681880951</v>
+        <v>584492.1681880951</v>
       </c>
       <c r="O15" s="4">
-        <v>0.016990063606421</v>
+        <v>16.990063606421</v>
       </c>
       <c r="P15" s="5">
         <v>34402</v>
@@ -1333,10 +1356,10 @@
         <v>694</v>
       </c>
       <c r="N16" s="5">
-        <v>673.6248841285706</v>
+        <v>673624.8841285706</v>
       </c>
       <c r="O16" s="4">
-        <v>0.02595256912192058</v>
+        <v>25.95256912192058</v>
       </c>
       <c r="P16" s="5">
         <v>25956</v>
@@ -1383,10 +1406,10 @@
         <v>694</v>
       </c>
       <c r="N17" s="5">
-        <v>2794.383126735687</v>
+        <v>2794383.126735687</v>
       </c>
       <c r="O17" s="4">
-        <v>0.03526881052537122</v>
+        <v>35.26881052537122</v>
       </c>
       <c r="P17" s="5">
         <v>79231</v>
@@ -1433,10 +1456,10 @@
         <v>694</v>
       </c>
       <c r="N18" s="5">
-        <v>1110.818125009537</v>
+        <v>1110818.125009537</v>
       </c>
       <c r="O18" s="4">
-        <v>0.02882920570474519</v>
+        <v>28.82920570474518</v>
       </c>
       <c r="P18" s="5">
         <v>38531</v>
@@ -1483,10 +1506,10 @@
         <v>694</v>
       </c>
       <c r="N19" s="5">
-        <v>3994.273916006088</v>
+        <v>3994273.916006088</v>
       </c>
       <c r="O19" s="4">
-        <v>0.08651981796140208</v>
+        <v>86.51981796140208</v>
       </c>
       <c r="P19" s="5">
         <v>46166</v>
@@ -1533,10 +1556,10 @@
         <v>694</v>
       </c>
       <c r="N20" s="5">
-        <v>2014.62038564682</v>
+        <v>2014620.38564682</v>
       </c>
       <c r="O20" s="4">
-        <v>0.07518362388590909</v>
+        <v>75.18362388590909</v>
       </c>
       <c r="P20" s="5">
         <v>26796</v>
@@ -1583,10 +1606,10 @@
         <v>691</v>
       </c>
       <c r="N21" s="5">
-        <v>19518.8764936924</v>
+        <v>19518876.4936924</v>
       </c>
       <c r="O21" s="4">
-        <v>0.3804255962752865</v>
+        <v>380.4255962752865</v>
       </c>
       <c r="P21" s="5">
         <v>51308</v>
@@ -1633,10 +1656,10 @@
         <v>691</v>
       </c>
       <c r="N22" s="5">
-        <v>5937.039171457291</v>
+        <v>5937039.171457291</v>
       </c>
       <c r="O22" s="4">
-        <v>0.1173281524733665</v>
+        <v>117.3281524733665</v>
       </c>
       <c r="P22" s="5">
         <v>50602</v>
@@ -1683,10 +1706,10 @@
         <v>694</v>
       </c>
       <c r="N23" s="5">
-        <v>5483.558859586716</v>
+        <v>5483558.859586716</v>
       </c>
       <c r="O23" s="4">
-        <v>0.09904377963671482</v>
+        <v>99.04377963671482</v>
       </c>
       <c r="P23" s="5">
         <v>55365</v>
@@ -1714,7 +1737,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1725,9 +1748,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
@@ -1761,8 +1790,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1784,34 +1821,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B3" s="4">
-        <v>0.8321407443193382</v>
+        <v>0.1747231270581385</v>
       </c>
       <c r="C3" s="4">
-        <v>0.8674598198247647</v>
+        <v>0.1730039562296326</v>
       </c>
       <c r="D3" s="4">
-        <v>0.8816938882364601</v>
+        <v>0.1772082199728205</v>
       </c>
       <c r="E3" s="4">
-        <v>94.2075271667108</v>
+        <v>98.65756692287309</v>
       </c>
       <c r="F3" s="4">
-        <v>89.41809029896298</v>
+        <v>98.44998402045353</v>
       </c>
       <c r="G3" s="5">
         <v>308</v>
       </c>
       <c r="H3" s="5">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="I3" s="5">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -1825,25 +1880,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1037121084844398</v>
+      </c>
+      <c r="O3" s="5">
+        <v>306</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1398895541236778</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1372648559656365</v>
+      </c>
+      <c r="R3" s="5">
+        <v>306</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2277425883118558</v>
+        <v>0.09178078059807288</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1881639175655634</v>
+        <v>0.04725108086251267</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2283346533398448</v>
+        <v>0.09178245260472866</v>
       </c>
       <c r="E4" s="4">
-        <v>96.45232230823363</v>
+        <v>98.74868050668539</v>
       </c>
       <c r="F4" s="4">
-        <v>94.2031647766721</v>
+        <v>98.82680513769948</v>
       </c>
       <c r="G4" s="5">
         <v>232</v>
@@ -1866,34 +1939,52 @@
       <c r="M4" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.05765184590726619</v>
+      </c>
+      <c r="O4" s="5">
+        <v>232</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1227985124646461</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.07982441935669711</v>
+      </c>
+      <c r="R4" s="5">
+        <v>228</v>
+      </c>
+      <c r="S4" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3139300394198666</v>
+        <v>0.05665666167141403</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3140613657901911</v>
+        <v>0.05665666167141403</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4210233009157211</v>
+        <v>0.06358868097321044</v>
       </c>
       <c r="E5" s="4">
-        <v>89.36191359660748</v>
+        <v>98.80753600141355</v>
       </c>
       <c r="F5" s="4">
-        <v>83.38947964786894</v>
+        <v>98.64268282053519</v>
       </c>
       <c r="G5" s="5">
         <v>154</v>
       </c>
       <c r="H5" s="5">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="I5" s="5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -1907,9 +1998,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.01754591749840116</v>
+      </c>
+      <c r="O5" s="5">
+        <v>154</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.04951980356588364</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.04951980356588364</v>
+      </c>
+      <c r="R5" s="5">
+        <v>154</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1920,6 +2029,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1927,7 +2037,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1938,9 +2048,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
@@ -1974,8 +2090,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1997,34 +2121,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2738266207663035</v>
+        <v>0.6818642686801094</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2778095307331276</v>
+        <v>0.689000376986189</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3246220851566339</v>
+        <v>0.478326652566046</v>
       </c>
       <c r="E3" s="4">
-        <v>98.81692287304533</v>
+        <v>93.04826164993702</v>
       </c>
       <c r="F3" s="4">
-        <v>95.65991894012066</v>
+        <v>90.51002339155767</v>
       </c>
       <c r="G3" s="5">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H3" s="5">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="I3" s="5">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2038,31 +2180,49 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.689000376986189</v>
+      </c>
+      <c r="O3" s="5">
+        <v>299</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1522358564051578</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1476393081384311</v>
+      </c>
+      <c r="R3" s="5">
+        <v>299</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1433743082669903</v>
+        <v>0.1070954113478725</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1006874808305819</v>
+        <v>0.06243687450106532</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1445406294253656</v>
+        <v>0.1062151984660457</v>
       </c>
       <c r="E4" s="4">
-        <v>99.72026741731176</v>
+        <v>97.94107253290926</v>
       </c>
       <c r="F4" s="4">
-        <v>98.18589446887295</v>
+        <v>97.332287399401</v>
       </c>
       <c r="G4" s="5">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H4" s="5">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
@@ -2079,37 +2239,55 @@
       <c r="M4" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.07817627081378893</v>
+      </c>
+      <c r="O4" s="5">
+        <v>231</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1309277763447348</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.08806674849899634</v>
+      </c>
+      <c r="R4" s="5">
+        <v>227</v>
+      </c>
+      <c r="S4" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B5" s="4">
-        <v>0.08728315307120971</v>
+        <v>0.7234713694326804</v>
       </c>
       <c r="C5" s="4">
-        <v>0.08728315307120971</v>
+        <v>0.711974522225548</v>
       </c>
       <c r="D5" s="4">
-        <v>0.07581835407295046</v>
+        <v>0.6363215259329524</v>
       </c>
       <c r="E5" s="4">
-        <v>98.94844950967402</v>
+        <v>93.86021075096713</v>
       </c>
       <c r="F5" s="4">
-        <v>96.7205613178767</v>
+        <v>91.36048602886363</v>
       </c>
       <c r="G5" s="5">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H5" s="5">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -2118,11 +2296,29 @@
         <v>0</v>
       </c>
       <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.7234713694326804</v>
+      </c>
+      <c r="O5" s="5">
+        <v>153</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1964927696729257</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1964927696729257</v>
+      </c>
+      <c r="R5" s="5">
+        <v>153</v>
+      </c>
+      <c r="S5" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2133,6 +2329,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2140,7 +2337,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2151,9 +2348,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
@@ -2187,8 +2390,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2210,34 +2421,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B3" s="4">
-        <v>0.8462270006915283</v>
+        <v>0.8321407443193382</v>
       </c>
       <c r="C3" s="4">
-        <v>0.8476709173087894</v>
+        <v>0.8674598198247647</v>
       </c>
       <c r="D3" s="4">
-        <v>0.694795103711473</v>
+        <v>0.8816938882364601</v>
       </c>
       <c r="E3" s="4">
-        <v>91.3951099920486</v>
+        <v>94.2075271667108</v>
       </c>
       <c r="F3" s="4">
-        <v>88.51412010807989</v>
+        <v>89.41809029896298</v>
       </c>
       <c r="G3" s="5">
         <v>308</v>
       </c>
       <c r="H3" s="5">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="I3" s="5">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2251,78 +2480,114 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.853089881921901</v>
+      </c>
+      <c r="O3" s="5">
+        <v>276</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2405115577537076</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2270938416167456</v>
+      </c>
+      <c r="R3" s="5">
+        <v>276</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2446580874894145</v>
+        <v>0.2277425883118558</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1951653401735169</v>
+        <v>0.1881639175655634</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2364057569690331</v>
+        <v>0.2283346533398448</v>
       </c>
       <c r="E4" s="4">
-        <v>95.9856615059817</v>
+        <v>96.45232230823363</v>
       </c>
       <c r="F4" s="4">
-        <v>95.92469914371684</v>
+        <v>94.2031647766721</v>
       </c>
       <c r="G4" s="5">
         <v>232</v>
       </c>
       <c r="H4" s="5">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="I4" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.09205577406635082</v>
+      </c>
+      <c r="O4" s="5">
+        <v>232</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1598206293975123</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1174353317568217</v>
+      </c>
+      <c r="R4" s="5">
+        <v>228</v>
+      </c>
+      <c r="S4" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B5" s="4">
-        <v>0.9899492052086923</v>
+        <v>0.3139300394198666</v>
       </c>
       <c r="C5" s="4">
-        <v>0.9831280781388622</v>
+        <v>0.3140613657901911</v>
       </c>
       <c r="D5" s="4">
-        <v>0.7890771976107257</v>
+        <v>0.4210233009157211</v>
       </c>
       <c r="E5" s="4">
-        <v>89.46660482374769</v>
+        <v>89.36191359660748</v>
       </c>
       <c r="F5" s="4">
-        <v>87.09404689270445</v>
+        <v>83.38947964786894</v>
       </c>
       <c r="G5" s="5">
         <v>154</v>
       </c>
       <c r="H5" s="5">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -2331,11 +2596,29 @@
         <v>0</v>
       </c>
       <c r="M5" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.2929196370526368</v>
+      </c>
+      <c r="O5" s="5">
+        <v>141</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.06167278742775525</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.06145314372164591</v>
+      </c>
+      <c r="R5" s="5">
+        <v>141</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2346,6 +2629,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2353,7 +2637,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2364,9 +2648,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
@@ -2400,8 +2690,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2423,34 +2721,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2830804467402234</v>
+        <v>0.2738266207663035</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2853519201416946</v>
+        <v>0.2778095307331276</v>
       </c>
       <c r="D3" s="4">
-        <v>0.323886257763056</v>
+        <v>0.3246220851566339</v>
       </c>
       <c r="E3" s="4">
-        <v>96.5624171746621</v>
+        <v>98.81692287304533</v>
       </c>
       <c r="F3" s="4">
-        <v>95.37639094686062</v>
+        <v>95.65991894012066</v>
       </c>
       <c r="G3" s="5">
         <v>308</v>
       </c>
       <c r="H3" s="5">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="I3" s="5">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2464,34 +2780,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.2431503031821704</v>
+      </c>
+      <c r="O3" s="5">
+        <v>284</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1609080366587531</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1532612936761197</v>
+      </c>
+      <c r="R3" s="5">
+        <v>284</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1673218983760813</v>
+        <v>0.1433743082669903</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1276746995745608</v>
+        <v>0.1006874808305819</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1695091176133655</v>
+        <v>0.1445406294253656</v>
       </c>
       <c r="E4" s="4">
-        <v>97.76873680506688</v>
+        <v>99.72026741731176</v>
       </c>
       <c r="F4" s="4">
-        <v>96.07131836766455</v>
+        <v>98.18589446887295</v>
       </c>
       <c r="G4" s="5">
         <v>232</v>
       </c>
       <c r="H4" s="5">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="I4" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
         <v>4</v>
@@ -2505,25 +2839,43 @@
       <c r="M4" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.004954208121248896</v>
+      </c>
+      <c r="O4" s="5">
+        <v>232</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1405788965578048</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09775611087875714</v>
+      </c>
+      <c r="R4" s="5">
+        <v>228</v>
+      </c>
+      <c r="S4" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2451542802485258</v>
+        <v>0.08728315307120971</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2451542802485258</v>
+        <v>0.08728315307120971</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2487570902219812</v>
+        <v>0.07581835407295046</v>
       </c>
       <c r="E5" s="4">
-        <v>98.4256559766764</v>
+        <v>98.94844950967402</v>
       </c>
       <c r="F5" s="4">
-        <v>97.38167872396068</v>
+        <v>96.7205613178767</v>
       </c>
       <c r="G5" s="5">
         <v>154</v>
@@ -2546,9 +2898,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.04693473124373062</v>
+      </c>
+      <c r="O5" s="5">
+        <v>154</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.07005391271023895</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.07005391271023895</v>
+      </c>
+      <c r="R5" s="5">
+        <v>154</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2559,6 +2929,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2566,7 +2937,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2577,9 +2948,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
@@ -2613,8 +2990,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2636,34 +3021,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2707869320104939</v>
+        <v>0.8462270006915283</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2667788879127853</v>
+        <v>0.8476709173087894</v>
       </c>
       <c r="D3" s="4">
-        <v>0.7133693183707697</v>
+        <v>0.694795103711473</v>
       </c>
       <c r="E3" s="4">
-        <v>81.51934799893969</v>
+        <v>91.3951099920486</v>
       </c>
       <c r="F3" s="4">
-        <v>72.92251372788267</v>
+        <v>88.51412010807989</v>
       </c>
       <c r="G3" s="5">
         <v>308</v>
       </c>
       <c r="H3" s="5">
-        <v>226</v>
+        <v>288</v>
       </c>
       <c r="I3" s="5">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2677,75 +3080,111 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.8387115364509898</v>
+      </c>
+      <c r="O3" s="5">
+        <v>288</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2334522486689607</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2338872204890554</v>
+      </c>
+      <c r="R3" s="5">
+        <v>288</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2950601331843201</v>
+        <v>0.2446580874894145</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2432562674319998</v>
+        <v>0.1951653401735169</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2515519348181883</v>
+        <v>0.2364057569690331</v>
       </c>
       <c r="E4" s="4">
-        <v>95.74404761904761</v>
+        <v>95.9856615059817</v>
       </c>
       <c r="F4" s="4">
-        <v>92.72916184525235</v>
+        <v>95.92469914371684</v>
       </c>
       <c r="G4" s="5">
         <v>232</v>
       </c>
       <c r="H4" s="5">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I4" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2373419884960072</v>
+      </c>
+      <c r="O4" s="5">
+        <v>227</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1508116504948084</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1049815757642049</v>
+      </c>
+      <c r="R4" s="5">
+        <v>223</v>
+      </c>
+      <c r="S4" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B5" s="4">
-        <v>1.339496908889708</v>
+        <v>0.9899492052086923</v>
       </c>
       <c r="C5" s="4">
-        <v>1.328681630729224</v>
+        <v>0.9831280781388622</v>
       </c>
       <c r="D5" s="4">
-        <v>1.191049086297091</v>
+        <v>0.7890771976107257</v>
       </c>
       <c r="E5" s="4">
-        <v>88.89809170421412</v>
+        <v>89.46660482374769</v>
       </c>
       <c r="F5" s="4">
-        <v>84.29551991632479</v>
+        <v>87.09404689270445</v>
       </c>
       <c r="G5" s="5">
         <v>154</v>
       </c>
       <c r="H5" s="5">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
         <v>1</v>
@@ -2759,9 +3198,27 @@
       <c r="M5" s="5">
         <v>1</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.9943860155639669</v>
+      </c>
+      <c r="O5" s="5">
+        <v>153</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2272079529865117</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2242271631713107</v>
+      </c>
+      <c r="R5" s="5">
+        <v>153</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2772,6 +3229,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2779,7 +3237,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2790,9 +3248,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
@@ -2826,8 +3290,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2849,34 +3321,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B3" s="4">
-        <v>0.261080916378004</v>
+        <v>0.2830804467402234</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2585053846904892</v>
+        <v>0.2853519201416946</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2319450181859722</v>
+        <v>0.323886257763056</v>
       </c>
       <c r="E3" s="4">
-        <v>97.87227228553762</v>
+        <v>96.5624171746621</v>
       </c>
       <c r="F3" s="4">
-        <v>97.26531857404312</v>
+        <v>95.37639094686062</v>
       </c>
       <c r="G3" s="5">
         <v>308</v>
       </c>
       <c r="H3" s="5">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="I3" s="5">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2890,34 +3380,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.2022987911914177</v>
+      </c>
+      <c r="O3" s="5">
+        <v>295</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2068722594079844</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.205586147650668</v>
+      </c>
+      <c r="R3" s="5">
+        <v>295</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1221664373184225</v>
+        <v>0.1673218983760813</v>
       </c>
       <c r="C4" s="4">
-        <v>0.07724447748285487</v>
+        <v>0.1276746995745608</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1199474344129966</v>
+        <v>0.1695091176133655</v>
       </c>
       <c r="E4" s="4">
-        <v>98.52465986394557</v>
+        <v>97.76873680506688</v>
       </c>
       <c r="F4" s="4">
-        <v>98.27967098665532</v>
+        <v>96.07131836766455</v>
       </c>
       <c r="G4" s="5">
         <v>232</v>
       </c>
       <c r="H4" s="5">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J4" s="5">
         <v>4</v>
@@ -2931,25 +3439,43 @@
       <c r="M4" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.02467098531829064</v>
+      </c>
+      <c r="O4" s="5">
+        <v>225</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1558554010642385</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1145141063014864</v>
+      </c>
+      <c r="R4" s="5">
+        <v>221</v>
+      </c>
+      <c r="S4" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2780137343733411</v>
+        <v>0.2451542802485258</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2780137343733411</v>
+        <v>0.2451542802485258</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2457748846587443</v>
+        <v>0.2487570902219812</v>
       </c>
       <c r="E5" s="4">
-        <v>96.90166975881262</v>
+        <v>98.4256559766764</v>
       </c>
       <c r="F5" s="4">
-        <v>95.6136145733459</v>
+        <v>97.38167872396068</v>
       </c>
       <c r="G5" s="5">
         <v>154</v>
@@ -2972,9 +3498,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.1964945202325618</v>
+      </c>
+      <c r="O5" s="5">
+        <v>154</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1743372584373704</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1743372584373704</v>
+      </c>
+      <c r="R5" s="5">
+        <v>154</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2985,6 +3529,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2992,7 +3537,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3003,9 +3548,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
@@ -3039,8 +3590,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3062,34 +3621,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2527479922885947</v>
+        <v>0.2707869320104939</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2372546561780849</v>
+        <v>0.2667788879127853</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2278703632308165</v>
+        <v>0.7133693183707697</v>
       </c>
       <c r="E3" s="4">
-        <v>98.02047442353469</v>
+        <v>81.51934799893969</v>
       </c>
       <c r="F3" s="4">
-        <v>97.05068421511662</v>
+        <v>72.92251372788267</v>
       </c>
       <c r="G3" s="5">
         <v>308</v>
       </c>
       <c r="H3" s="5">
-        <v>294</v>
+        <v>226</v>
       </c>
       <c r="I3" s="5">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -3103,34 +3680,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.0181111939903482</v>
+      </c>
+      <c r="O3" s="5">
+        <v>226</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2680748283878875</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2651761754744615</v>
+      </c>
+      <c r="R3" s="5">
+        <v>226</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1197622943204188</v>
+        <v>0.2950601331843201</v>
       </c>
       <c r="C4" s="4">
-        <v>0.07514789742372661</v>
+        <v>0.2432562674319998</v>
       </c>
       <c r="D4" s="4">
-        <v>0.118803114407631</v>
+        <v>0.2515519348181883</v>
       </c>
       <c r="E4" s="4">
-        <v>99.54477480647428</v>
+        <v>95.74404761904761</v>
       </c>
       <c r="F4" s="4">
-        <v>99.2257289979173</v>
+        <v>92.72916184525235</v>
       </c>
       <c r="G4" s="5">
         <v>232</v>
       </c>
       <c r="H4" s="5">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J4" s="5">
         <v>4</v>
@@ -3144,37 +3739,55 @@
       <c r="M4" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2789129502726771</v>
+      </c>
+      <c r="O4" s="5">
+        <v>225</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1997622601065639</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1558017825781094</v>
+      </c>
+      <c r="R4" s="5">
+        <v>221</v>
+      </c>
+      <c r="S4" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B5" s="4">
-        <v>0.0791444261563396</v>
+        <v>1.339496908889708</v>
       </c>
       <c r="C5" s="4">
-        <v>0.0791444261563396</v>
+        <v>1.328681630729224</v>
       </c>
       <c r="D5" s="4">
-        <v>0.07944575545678956</v>
+        <v>1.191049086297091</v>
       </c>
       <c r="E5" s="4">
-        <v>99.36721441823484</v>
+        <v>88.89809170421412</v>
       </c>
       <c r="F5" s="4">
-        <v>98.9207269240827</v>
+        <v>84.29551991632479</v>
       </c>
       <c r="G5" s="5">
         <v>154</v>
       </c>
       <c r="H5" s="5">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -3183,11 +3796,29 @@
         <v>0</v>
       </c>
       <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-1.340250262819442</v>
+      </c>
+      <c r="O5" s="5">
+        <v>152</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2728727075613891</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.275244678369006</v>
+      </c>
+      <c r="R5" s="5">
+        <v>152</v>
+      </c>
+      <c r="S5" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3198,6 +3829,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3205,7 +3837,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3216,9 +3848,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
@@ -3252,8 +3890,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3275,37 +3921,55 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B3" s="4">
-        <v>2.070973085758099</v>
+        <v>0.261080916378004</v>
       </c>
       <c r="C3" s="4">
-        <v>1.874227953155458</v>
+        <v>0.2585053846904892</v>
       </c>
       <c r="D3" s="4">
-        <v>1.797790175237083</v>
+        <v>0.2319450181859722</v>
       </c>
       <c r="E3" s="4">
-        <v>93.05581323438467</v>
+        <v>97.87227228553762</v>
       </c>
       <c r="F3" s="4">
-        <v>84.23563293529746</v>
+        <v>97.26531857404312</v>
       </c>
       <c r="G3" s="5">
         <v>308</v>
       </c>
       <c r="H3" s="5">
-        <v>29</v>
+        <v>301</v>
       </c>
       <c r="I3" s="5">
-        <v>157</v>
+        <v>7</v>
       </c>
       <c r="J3" s="5">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -3314,36 +3978,54 @@
         <v>0</v>
       </c>
       <c r="M3" s="5">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.2558399698652549</v>
+      </c>
+      <c r="O3" s="5">
+        <v>301</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.13580061670645</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1362613564187887</v>
+      </c>
+      <c r="R3" s="5">
+        <v>301</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2583116013055338</v>
+        <v>0.1221664373184225</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2202070977602484</v>
+        <v>0.07724447748285487</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2966879504641166</v>
+        <v>0.1199474344129966</v>
       </c>
       <c r="E4" s="4">
-        <v>95.78157987332864</v>
+        <v>98.52465986394557</v>
       </c>
       <c r="F4" s="4">
-        <v>90.06359446115874</v>
+        <v>98.27967098665532</v>
       </c>
       <c r="G4" s="5">
         <v>232</v>
       </c>
       <c r="H4" s="5">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="I4" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>4</v>
@@ -3357,37 +4039,55 @@
       <c r="M4" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.106286276991591</v>
+      </c>
+      <c r="O4" s="5">
+        <v>231</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1353074557006402</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09301605303189653</v>
+      </c>
+      <c r="R4" s="5">
+        <v>227</v>
+      </c>
+      <c r="S4" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B5" s="4">
-        <v>1.46973592481627</v>
+        <v>0.2780137343733411</v>
       </c>
       <c r="C5" s="4">
-        <v>1.374414752447634</v>
+        <v>0.2780137343733411</v>
       </c>
       <c r="D5" s="4">
-        <v>1.232207886298357</v>
+        <v>0.2457748846587443</v>
       </c>
       <c r="E5" s="4">
-        <v>89.53949112112379</v>
+        <v>96.90166975881262</v>
       </c>
       <c r="F5" s="4">
-        <v>79.63036404311546</v>
+        <v>95.6136145733459</v>
       </c>
       <c r="G5" s="5">
         <v>154</v>
       </c>
       <c r="H5" s="5">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="I5" s="5">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -3396,11 +4096,29 @@
         <v>0</v>
       </c>
       <c r="M5" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.2780137343733411</v>
+      </c>
+      <c r="O5" s="5">
+        <v>154</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.06350181927233636</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.06350181927233636</v>
+      </c>
+      <c r="R5" s="5">
+        <v>154</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3411,6 +4129,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3418,7 +4137,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3429,9 +4148,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
@@ -3465,8 +4190,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3488,40 +4221,58 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1975104640573938</v>
+        <v>0.2527479922885947</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2006419261653666</v>
+        <v>0.2372546561780849</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1914220425803316</v>
+        <v>0.2278703632308165</v>
       </c>
       <c r="E3" s="4">
-        <v>95.93349677533341</v>
+        <v>98.02047442353469</v>
       </c>
       <c r="F3" s="4">
-        <v>95.55401812952144</v>
+        <v>97.05068421511662</v>
       </c>
       <c r="G3" s="5">
         <v>308</v>
       </c>
       <c r="H3" s="5">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I3" s="5">
         <v>14</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
         <v>0</v>
@@ -3529,25 +4280,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1630816105324231</v>
+      </c>
+      <c r="O3" s="5">
+        <v>294</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2449112875908699</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2368105660439171</v>
+      </c>
+      <c r="R3" s="5">
+        <v>294</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1599845455341449</v>
+        <v>0.1197622943204188</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1130595947469152</v>
+        <v>0.07514789742372661</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1616647496227532</v>
+        <v>0.118803114407631</v>
       </c>
       <c r="E4" s="4">
-        <v>96.97601454374851</v>
+        <v>99.54477480647428</v>
       </c>
       <c r="F4" s="4">
-        <v>97.30535948468719</v>
+        <v>99.2257289979173</v>
       </c>
       <c r="G4" s="5">
         <v>232</v>
@@ -3570,25 +4339,43 @@
       <c r="M4" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1139141107467376</v>
+      </c>
+      <c r="O4" s="5">
+        <v>232</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1312249869931747</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.08881018313892969</v>
+      </c>
+      <c r="R4" s="5">
+        <v>228</v>
+      </c>
+      <c r="S4" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2468528890391986</v>
+        <v>0.0791444261563396</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2468528890391986</v>
+        <v>0.0791444261563396</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2386746945211434</v>
+        <v>0.07944575545678956</v>
       </c>
       <c r="E5" s="4">
-        <v>95.3971198869158</v>
+        <v>99.36721441823484</v>
       </c>
       <c r="F5" s="4">
-        <v>95.16902001801333</v>
+        <v>98.9207269240827</v>
       </c>
       <c r="G5" s="5">
         <v>154</v>
@@ -3611,9 +4398,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.007278023348592282</v>
+      </c>
+      <c r="O5" s="5">
+        <v>154</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.08152644095140034</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.08152644095140034</v>
+      </c>
+      <c r="R5" s="5">
+        <v>154</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3624,6 +4429,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3631,7 +4437,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3642,9 +4448,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
@@ -3678,8 +4490,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3701,75 +4521,111 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B3" s="4">
-        <v>0.496758930764291</v>
+        <v>2.070973085758099</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4892757986095585</v>
+        <v>1.874227953155458</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4265841547080588</v>
+        <v>1.797790175237083</v>
       </c>
       <c r="E3" s="4">
-        <v>95.31208587331076</v>
+        <v>93.05581323438467</v>
       </c>
       <c r="F3" s="4">
-        <v>94.4005127981637</v>
+        <v>84.23563293529746</v>
       </c>
       <c r="G3" s="5">
         <v>308</v>
       </c>
       <c r="H3" s="5">
-        <v>271</v>
+        <v>29</v>
       </c>
       <c r="I3" s="5">
-        <v>36</v>
+        <v>157</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>122</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>122</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-2.176216331691623</v>
+      </c>
+      <c r="O3" s="5">
+        <v>151</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2321551062586826</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1648517515010344</v>
+      </c>
+      <c r="R3" s="5">
+        <v>151</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2661359212747671</v>
+        <v>0.2583116013055338</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2216834840300693</v>
+        <v>0.2202070977602484</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2626446949183981</v>
+        <v>0.2966879504641166</v>
       </c>
       <c r="E4" s="4">
-        <v>97.23610133708655</v>
+        <v>95.78157987332864</v>
       </c>
       <c r="F4" s="4">
-        <v>97.41957880120371</v>
+        <v>90.06359446115874</v>
       </c>
       <c r="G4" s="5">
         <v>232</v>
       </c>
       <c r="H4" s="5">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J4" s="5">
         <v>4</v>
@@ -3783,34 +4639,52 @@
       <c r="M4" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.09895913131356285</v>
+      </c>
+      <c r="O4" s="5">
+        <v>225</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2070214907310166</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1641380610247808</v>
+      </c>
+      <c r="R4" s="5">
+        <v>221</v>
+      </c>
+      <c r="S4" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B5" s="4">
-        <v>0.5392476881937542</v>
+        <v>1.46973592481627</v>
       </c>
       <c r="C5" s="4">
-        <v>0.5279209068087143</v>
+        <v>1.374414752447634</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4803748948074247</v>
+        <v>1.232207886298357</v>
       </c>
       <c r="E5" s="4">
-        <v>93.48860323350121</v>
+        <v>89.53949112112379</v>
       </c>
       <c r="F5" s="4">
-        <v>92.45845317992908</v>
+        <v>79.63036404311546</v>
       </c>
       <c r="G5" s="5">
         <v>154</v>
       </c>
       <c r="H5" s="5">
-        <v>152</v>
+        <v>106</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="J5" s="5">
         <v>1</v>
@@ -3824,9 +4698,27 @@
       <c r="M5" s="5">
         <v>1</v>
       </c>
+      <c r="N5" s="4">
+        <v>-1.391895791187406</v>
+      </c>
+      <c r="O5" s="5">
+        <v>107</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2879128843864758</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2911453713384908</v>
+      </c>
+      <c r="R5" s="5">
+        <v>107</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3837,12 +4729,2970 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P23"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>93.65994236311239</v>
+      </c>
+      <c r="C3" s="3">
+        <v>5.475504322766571</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0.8645533141210375</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0.1440922190201729</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.1440922190201729</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0.5763688760806917</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.1790751867936757</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.158785223829491</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.1721234791840562</v>
+      </c>
+      <c r="K3" s="4">
+        <v>94.82228626320787</v>
+      </c>
+      <c r="L3" s="4">
+        <v>95.40748763772663</v>
+      </c>
+      <c r="M3" s="5">
+        <v>694</v>
+      </c>
+      <c r="N3" s="5">
+        <v>1913901.945829391</v>
+      </c>
+      <c r="O3" s="4">
+        <v>41.93291148129774</v>
+      </c>
+      <c r="P3" s="5">
+        <v>45642</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>91.93083573487031</v>
+      </c>
+      <c r="C4" s="3">
+        <v>7.204610951008646</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0.8645533141210375</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0.2881844380403458</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.5763688760806917</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.2010530930164579</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.1853927391303593</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.2141635307746295</v>
+      </c>
+      <c r="K4" s="4">
+        <v>94.63021231547464</v>
+      </c>
+      <c r="L4" s="4">
+        <v>93.43145787800886</v>
+      </c>
+      <c r="M4" s="5">
+        <v>694</v>
+      </c>
+      <c r="N4" s="5">
+        <v>2322240.045785904</v>
+      </c>
+      <c r="O4" s="4">
+        <v>42.67176357997656</v>
+      </c>
+      <c r="P4" s="5">
+        <v>54421</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>68.44380403458213</v>
+      </c>
+      <c r="C5" s="3">
+        <v>30.40345821325649</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1.152737752161383</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0.5763688760806917</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.5763688760806917</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.2297292069134943</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.1931915021795235</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.3248375495630413</v>
+      </c>
+      <c r="K5" s="4">
+        <v>90.82005136348444</v>
+      </c>
+      <c r="L5" s="4">
+        <v>87.77354956836807</v>
+      </c>
+      <c r="M5" s="5">
+        <v>694</v>
+      </c>
+      <c r="N5" s="5">
+        <v>7262275.715112686</v>
+      </c>
+      <c r="O5" s="4">
+        <v>91.90776307772613</v>
+      </c>
+      <c r="P5" s="5">
+        <v>79017</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>99.13169319826338</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.2894356005788712</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.5788712011577424</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0.5788712011577424</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.1556224834628375</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.1418271308860014</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.1608892537850728</v>
+      </c>
+      <c r="K6" s="4">
+        <v>97.74112249820332</v>
+      </c>
+      <c r="L6" s="4">
+        <v>96.52115567038051</v>
+      </c>
+      <c r="M6" s="5">
+        <v>691</v>
+      </c>
+      <c r="N6" s="5">
+        <v>5195254.918575287</v>
+      </c>
+      <c r="O6" s="4">
+        <v>146.7295991915522</v>
+      </c>
+      <c r="P6" s="5">
+        <v>35407</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>73.66136034732273</v>
+      </c>
+      <c r="C7" s="3">
+        <v>23.44428364688857</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2.894356005788712</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>2.31548480463097</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.5788712011577424</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.457633023654902</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.2236730956289225</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.3028114932141261</v>
+      </c>
+      <c r="K7" s="4">
+        <v>88.20874804335618</v>
+      </c>
+      <c r="L7" s="4">
+        <v>87.53887469769485</v>
+      </c>
+      <c r="M7" s="5">
+        <v>691</v>
+      </c>
+      <c r="N7" s="5">
+        <v>7333776.261329651</v>
+      </c>
+      <c r="O7" s="4">
+        <v>100.4778290061468</v>
+      </c>
+      <c r="P7" s="5">
+        <v>72989</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>99.13544668587896</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.2881844380403458</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.5763688760806917</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0.5763688760806917</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.1141228923790154</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.0985887547790084</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.1141869109013268</v>
+      </c>
+      <c r="K8" s="4">
+        <v>98.72130408359311</v>
+      </c>
+      <c r="L8" s="4">
+        <v>98.6187132919429</v>
+      </c>
+      <c r="M8" s="5">
+        <v>694</v>
+      </c>
+      <c r="N8" s="5">
+        <v>6903975.885152817</v>
+      </c>
+      <c r="O8" s="4">
+        <v>269.8974153695394</v>
+      </c>
+      <c r="P8" s="5">
+        <v>25580</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>98.26338639652677</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1.157742402315485</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.5788712011577424</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0.5788712011577424</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.1549118929261575</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.1387315151732263</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.2026670140428191</v>
+      </c>
+      <c r="K9" s="4">
+        <v>94.86369945952238</v>
+      </c>
+      <c r="L9" s="4">
+        <v>92.97900135005213</v>
+      </c>
+      <c r="M9" s="5">
+        <v>691</v>
+      </c>
+      <c r="N9" s="5">
+        <v>1410215.593099594</v>
+      </c>
+      <c r="O9" s="4">
+        <v>26.47248208405313</v>
+      </c>
+      <c r="P9" s="5">
+        <v>53271</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>92.93948126801152</v>
+      </c>
+      <c r="C10" s="3">
+        <v>6.484149855907781</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.5763688760806917</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0.5763688760806917</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.1738523848303158</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.1521210064984949</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.1787987858484355</v>
+      </c>
+      <c r="K10" s="4">
+        <v>93.88269717108743</v>
+      </c>
+      <c r="L10" s="4">
+        <v>89.67995087325693</v>
+      </c>
+      <c r="M10" s="5">
+        <v>694</v>
+      </c>
+      <c r="N10" s="5">
+        <v>7690494.214773178</v>
+      </c>
+      <c r="O10" s="4">
+        <v>123.6731991311781</v>
+      </c>
+      <c r="P10" s="5">
+        <v>62184</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>95.96541786743515</v>
+      </c>
+      <c r="C11" s="3">
+        <v>3.45821325648415</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.5763688760806917</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0.5763688760806917</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.1339514147689963</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.115019374236864</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.1402678547453275</v>
+      </c>
+      <c r="K11" s="4">
+        <v>99.14809151326234</v>
+      </c>
+      <c r="L11" s="4">
+        <v>96.73969595574765</v>
+      </c>
+      <c r="M11" s="5">
+        <v>694</v>
+      </c>
+      <c r="N11" s="5">
+        <v>4325875.496149063</v>
+      </c>
+      <c r="O11" s="4">
+        <v>124.2425037667029</v>
+      </c>
+      <c r="P11" s="5">
+        <v>34818</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>95.67723342939482</v>
+      </c>
+      <c r="C12" s="3">
+        <v>3.45821325648415</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0.8645533141210375</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0.2881844380403458</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.5763688760806917</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.2044403750212655</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.1883692272010183</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.2265662277804357</v>
+      </c>
+      <c r="K12" s="4">
+        <v>92.50176439451883</v>
+      </c>
+      <c r="L12" s="4">
+        <v>90.67631472061588</v>
+      </c>
+      <c r="M12" s="5">
+        <v>694</v>
+      </c>
+      <c r="N12" s="5">
+        <v>9791068.883657455</v>
+      </c>
+      <c r="O12" s="4">
+        <v>156.2845198432131</v>
+      </c>
+      <c r="P12" s="5">
+        <v>62649</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>96.54178674351584</v>
+      </c>
+      <c r="C13" s="3">
+        <v>2.881844380403458</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0.5763688760806917</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.5763688760806917</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.1825980500632818</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.1683633863416875</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.1918596182313367</v>
+      </c>
+      <c r="K13" s="4">
+        <v>97.37913897547494</v>
+      </c>
+      <c r="L13" s="4">
+        <v>96.05367838101061</v>
+      </c>
+      <c r="M13" s="5">
+        <v>694</v>
+      </c>
+      <c r="N13" s="5">
+        <v>2954475.812911987</v>
+      </c>
+      <c r="O13" s="4">
+        <v>94.35903717262264</v>
+      </c>
+      <c r="P13" s="5">
+        <v>31311</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>86.31123919308358</v>
+      </c>
+      <c r="C14" s="3">
+        <v>13.11239193083573</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0.5763688760806917</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0.5763688760806917</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.246303009297761</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.2273776305827702</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.4416779432224178</v>
+      </c>
+      <c r="K14" s="4">
+        <v>87.91193710913753</v>
+      </c>
+      <c r="L14" s="4">
+        <v>82.06744934207576</v>
+      </c>
+      <c r="M14" s="5">
+        <v>694</v>
+      </c>
+      <c r="N14" s="5">
+        <v>4529314.520359039</v>
+      </c>
+      <c r="O14" s="4">
+        <v>54.14148870218917</v>
+      </c>
+      <c r="P14" s="5">
+        <v>83657</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>98.27089337175792</v>
+      </c>
+      <c r="C15" s="3">
+        <v>1.152737752161383</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0.5763688760806917</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.5763688760806917</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.1195925069684077</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.1054378188977063</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.1201306654782267</v>
+      </c>
+      <c r="K15" s="4">
+        <v>97.87498284616444</v>
+      </c>
+      <c r="L15" s="4">
+        <v>97.23789399712578</v>
+      </c>
+      <c r="M15" s="5">
+        <v>694</v>
+      </c>
+      <c r="N15" s="5">
+        <v>584492.1681880951</v>
+      </c>
+      <c r="O15" s="4">
+        <v>16.990063606421</v>
+      </c>
+      <c r="P15" s="5">
+        <v>34402</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>97.40634005763688</v>
+      </c>
+      <c r="C16" s="3">
+        <v>2.017291066282421</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.5763688760806917</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.5763688760806917</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.1706512182520463</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.1515178995253006</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.1702979141645274</v>
+      </c>
+      <c r="K16" s="4">
+        <v>98.82888313826874</v>
+      </c>
+      <c r="L16" s="4">
+        <v>98.19275477245341</v>
+      </c>
+      <c r="M16" s="5">
+        <v>694</v>
+      </c>
+      <c r="N16" s="5">
+        <v>673624.8841285706</v>
+      </c>
+      <c r="O16" s="4">
+        <v>25.95256912192058</v>
+      </c>
+      <c r="P16" s="5">
+        <v>25956</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>69.02017291066282</v>
+      </c>
+      <c r="C17" s="3">
+        <v>30.40345821325649</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0.5763688760806917</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.5763688760806917</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.2361258541394631</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.1927341976959317</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.3059888861468635</v>
+      </c>
+      <c r="K17" s="4">
+        <v>93.1867415554118</v>
+      </c>
+      <c r="L17" s="4">
+        <v>85.1619667459664</v>
+      </c>
+      <c r="M17" s="5">
+        <v>694</v>
+      </c>
+      <c r="N17" s="5">
+        <v>2794383.126735687</v>
+      </c>
+      <c r="O17" s="4">
+        <v>35.26881052537122</v>
+      </c>
+      <c r="P17" s="5">
+        <v>79231</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="25" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="3">
+        <v>97.26224783861672</v>
+      </c>
+      <c r="C18" s="3">
+        <v>2.017291066282421</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0.7204610951008645</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0.1440922190201729</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0.5763688760806917</v>
+      </c>
+      <c r="H18" s="4">
+        <v>0.1768371273723198</v>
+      </c>
+      <c r="I18" s="4">
+        <v>0.1630723834853231</v>
+      </c>
+      <c r="J18" s="4">
+        <v>0.1799858771033051</v>
+      </c>
+      <c r="K18" s="4">
+        <v>96.16298104256124</v>
+      </c>
+      <c r="L18" s="4">
+        <v>96.05404908805984</v>
+      </c>
+      <c r="M18" s="5">
+        <v>694</v>
+      </c>
+      <c r="N18" s="5">
+        <v>1110818.125009537</v>
+      </c>
+      <c r="O18" s="4">
+        <v>28.82920570474518</v>
+      </c>
+      <c r="P18" s="5">
+        <v>38531</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="25" customHeight="1">
+      <c r="A19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="3">
+        <v>93.80403458213257</v>
+      </c>
+      <c r="C19" s="3">
+        <v>5.475504322766571</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0.7204610951008645</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0.1440922190201729</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0.5763688760806917</v>
+      </c>
+      <c r="H19" s="4">
+        <v>0.1519153742868529</v>
+      </c>
+      <c r="I19" s="4">
+        <v>0.1344825503394707</v>
+      </c>
+      <c r="J19" s="4">
+        <v>0.1597716841239765</v>
+      </c>
+      <c r="K19" s="4">
+        <v>95.55063812268486</v>
+      </c>
+      <c r="L19" s="4">
+        <v>94.97882134498975</v>
+      </c>
+      <c r="M19" s="5">
+        <v>694</v>
+      </c>
+      <c r="N19" s="5">
+        <v>3994273.916006088</v>
+      </c>
+      <c r="O19" s="4">
+        <v>86.51981796140208</v>
+      </c>
+      <c r="P19" s="5">
+        <v>46166</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="25" customHeight="1">
+      <c r="A20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="3">
+        <v>96.39769452449568</v>
+      </c>
+      <c r="C20" s="3">
+        <v>3.025936599423631</v>
+      </c>
+      <c r="D20" s="3">
+        <v>0.5763688760806917</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0.5763688760806917</v>
+      </c>
+      <c r="H20" s="4">
+        <v>0.1322157128016992</v>
+      </c>
+      <c r="I20" s="4">
+        <v>0.1131597729289562</v>
+      </c>
+      <c r="J20" s="4">
+        <v>0.1373656956960403</v>
+      </c>
+      <c r="K20" s="4">
+        <v>99.59757101687941</v>
+      </c>
+      <c r="L20" s="4">
+        <v>97.87592918528291</v>
+      </c>
+      <c r="M20" s="5">
+        <v>694</v>
+      </c>
+      <c r="N20" s="5">
+        <v>2014620.38564682</v>
+      </c>
+      <c r="O20" s="4">
+        <v>75.18362388590909</v>
+      </c>
+      <c r="P20" s="5">
+        <v>26796</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="25" customHeight="1">
+      <c r="A21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="3">
+        <v>99.27641099855282</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0.1447178002894356</v>
+      </c>
+      <c r="D21" s="3">
+        <v>0.5788712011577424</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0.5788712011577424</v>
+      </c>
+      <c r="H21" s="4">
+        <v>0.1349684804848136</v>
+      </c>
+      <c r="I21" s="4">
+        <v>0.1204863798305592</v>
+      </c>
+      <c r="J21" s="4">
+        <v>0.137604076417054</v>
+      </c>
+      <c r="K21" s="4">
+        <v>91.44068046900384</v>
+      </c>
+      <c r="L21" s="4">
+        <v>93.05204013248125</v>
+      </c>
+      <c r="M21" s="5">
+        <v>691</v>
+      </c>
+      <c r="N21" s="5">
+        <v>19518876.4936924</v>
+      </c>
+      <c r="O21" s="4">
+        <v>380.4255962752865</v>
+      </c>
+      <c r="P21" s="5">
+        <v>51308</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="25" customHeight="1">
+      <c r="A22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="3">
+        <v>98.11866859623734</v>
+      </c>
+      <c r="C22" s="3">
+        <v>1.30246020260492</v>
+      </c>
+      <c r="D22" s="3">
+        <v>0.5788712011577424</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0.5788712011577424</v>
+      </c>
+      <c r="H22" s="4">
+        <v>0.1424717044585462</v>
+      </c>
+      <c r="I22" s="4">
+        <v>0.1277575815170843</v>
+      </c>
+      <c r="J22" s="4">
+        <v>0.1414489677519044</v>
+      </c>
+      <c r="K22" s="4">
+        <v>91.18117290331443</v>
+      </c>
+      <c r="L22" s="4">
+        <v>92.90546074974858</v>
+      </c>
+      <c r="M22" s="5">
+        <v>691</v>
+      </c>
+      <c r="N22" s="5">
+        <v>5937039.171457291</v>
+      </c>
+      <c r="O22" s="4">
+        <v>117.3281524733665</v>
+      </c>
+      <c r="P22" s="5">
+        <v>50602</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="25" customHeight="1">
+      <c r="A23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="3">
+        <v>98.55907780979827</v>
+      </c>
+      <c r="C23" s="3">
+        <v>0.7204610951008645</v>
+      </c>
+      <c r="D23" s="3">
+        <v>0.7204610951008645</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
+        <v>0.1440922190201729</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0.5763688760806917</v>
+      </c>
+      <c r="H23" s="4">
+        <v>0.1305250916553865</v>
+      </c>
+      <c r="I23" s="4">
+        <v>0.1159481134847588</v>
+      </c>
+      <c r="J23" s="4">
+        <v>0.1311817536967869</v>
+      </c>
+      <c r="K23" s="4">
+        <v>95.57612382128647</v>
+      </c>
+      <c r="L23" s="4">
+        <v>92.648589056728</v>
+      </c>
+      <c r="M23" s="5">
+        <v>694</v>
+      </c>
+      <c r="N23" s="5">
+        <v>5483558.859586716</v>
+      </c>
+      <c r="O23" s="4">
+        <v>99.04377963671482</v>
+      </c>
+      <c r="P23" s="5">
+        <v>55365</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.1975104640573938</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2006419261653666</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.1914220425803316</v>
+      </c>
+      <c r="E3" s="4">
+        <v>95.93349677533341</v>
+      </c>
+      <c r="F3" s="4">
+        <v>95.55401812952144</v>
+      </c>
+      <c r="G3" s="5">
+        <v>308</v>
+      </c>
+      <c r="H3" s="5">
+        <v>293</v>
+      </c>
+      <c r="I3" s="5">
+        <v>14</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.04509766402599594</v>
+      </c>
+      <c r="O3" s="5">
+        <v>293</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.191379977891472</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1947954898256147</v>
+      </c>
+      <c r="R3" s="5">
+        <v>293</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.1599845455341449</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1130595947469152</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.1616647496227532</v>
+      </c>
+      <c r="E4" s="4">
+        <v>96.97601454374851</v>
+      </c>
+      <c r="F4" s="4">
+        <v>97.30535948468719</v>
+      </c>
+      <c r="G4" s="5">
+        <v>232</v>
+      </c>
+      <c r="H4" s="5">
+        <v>228</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>4</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>4</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.1394185223740971</v>
+      </c>
+      <c r="O4" s="5">
+        <v>232</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1459198329633928</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1011940718218358</v>
+      </c>
+      <c r="R4" s="5">
+        <v>228</v>
+      </c>
+      <c r="S4" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.2468528890391986</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.2468528890391986</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.2386746945211434</v>
+      </c>
+      <c r="E5" s="4">
+        <v>95.3971198869158</v>
+      </c>
+      <c r="F5" s="4">
+        <v>95.16902001801333</v>
+      </c>
+      <c r="G5" s="5">
+        <v>154</v>
+      </c>
+      <c r="H5" s="5">
+        <v>154</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.1916165400422406</v>
+      </c>
+      <c r="O5" s="5">
+        <v>154</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1943281295994118</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1943281295994118</v>
+      </c>
+      <c r="R5" s="5">
+        <v>154</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.496758930764291</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.4892757986095585</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.4265841547080588</v>
+      </c>
+      <c r="E3" s="4">
+        <v>95.31208587331076</v>
+      </c>
+      <c r="F3" s="4">
+        <v>94.4005127981637</v>
+      </c>
+      <c r="G3" s="5">
+        <v>308</v>
+      </c>
+      <c r="H3" s="5">
+        <v>271</v>
+      </c>
+      <c r="I3" s="5">
+        <v>36</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.4871476295408509</v>
+      </c>
+      <c r="O3" s="5">
+        <v>271</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.185457038455609</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1827060025060375</v>
+      </c>
+      <c r="R3" s="5">
+        <v>271</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.2661359212747671</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2216834840300693</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2626446949183981</v>
+      </c>
+      <c r="E4" s="4">
+        <v>97.23610133708655</v>
+      </c>
+      <c r="F4" s="4">
+        <v>97.41957880120371</v>
+      </c>
+      <c r="G4" s="5">
+        <v>232</v>
+      </c>
+      <c r="H4" s="5">
+        <v>227</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>4</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>4</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.2662156975952035</v>
+      </c>
+      <c r="O4" s="5">
+        <v>231</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1322630431246965</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09056257893966028</v>
+      </c>
+      <c r="R4" s="5">
+        <v>227</v>
+      </c>
+      <c r="S4" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.5392476881937542</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.5279209068087143</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.4803748948074247</v>
+      </c>
+      <c r="E5" s="4">
+        <v>93.48860323350121</v>
+      </c>
+      <c r="F5" s="4">
+        <v>92.45845317992908</v>
+      </c>
+      <c r="G5" s="5">
+        <v>154</v>
+      </c>
+      <c r="H5" s="5">
+        <v>152</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.5382972483673754</v>
+      </c>
+      <c r="O5" s="5">
+        <v>153</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1144381552325891</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.114229465180107</v>
+      </c>
+      <c r="R5" s="5">
+        <v>153</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.3016267141979416</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.3090756370152416</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.3341605661492484</v>
+      </c>
+      <c r="E3" s="4">
+        <v>99.32083222899551</v>
+      </c>
+      <c r="F3" s="4">
+        <v>96.84117057439258</v>
+      </c>
+      <c r="G3" s="5">
+        <v>308</v>
+      </c>
+      <c r="H3" s="5">
+        <v>287</v>
+      </c>
+      <c r="I3" s="5">
+        <v>21</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.2626532384357471</v>
+      </c>
+      <c r="O3" s="5">
+        <v>287</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1728659889978673</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1664594840548649</v>
+      </c>
+      <c r="R3" s="5">
+        <v>287</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.1267023664415422</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.0824079300066542</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.1297698425278807</v>
+      </c>
+      <c r="E4" s="4">
+        <v>99.95073891625616</v>
+      </c>
+      <c r="F4" s="4">
+        <v>99.07096158296689</v>
+      </c>
+      <c r="G4" s="5">
+        <v>232</v>
+      </c>
+      <c r="H4" s="5">
+        <v>228</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>4</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>4</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.005244266402499206</v>
+      </c>
+      <c r="O4" s="5">
+        <v>232</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1305145838986274</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.08637903314548651</v>
+      </c>
+      <c r="R4" s="5">
+        <v>228</v>
+      </c>
+      <c r="S4" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.12749929934742</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.12749929934742</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.1528067144097058</v>
+      </c>
+      <c r="E5" s="4">
+        <v>99.61900344553409</v>
+      </c>
+      <c r="F5" s="4">
+        <v>98.145137859903</v>
+      </c>
+      <c r="G5" s="5">
+        <v>154</v>
+      </c>
+      <c r="H5" s="5">
+        <v>154</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.1004790515634449</v>
+      </c>
+      <c r="O5" s="5">
+        <v>154</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.05347790005554887</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.05347790005554887</v>
+      </c>
+      <c r="R5" s="5">
+        <v>154</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.7128454672845418</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.7136767709091462</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.7232942864125901</v>
+      </c>
+      <c r="E3" s="4">
+        <v>92.18008375988853</v>
+      </c>
+      <c r="F3" s="4">
+        <v>93.9202719541769</v>
+      </c>
+      <c r="G3" s="5">
+        <v>307</v>
+      </c>
+      <c r="H3" s="5">
+        <v>306</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.6964471507120458</v>
+      </c>
+      <c r="O3" s="5">
+        <v>306</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1661963738318826</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1659617848818025</v>
+      </c>
+      <c r="R3" s="5">
+        <v>306</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.21800208731579</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1777981803159182</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2179079735064522</v>
+      </c>
+      <c r="E4" s="4">
+        <v>94.10857849633359</v>
+      </c>
+      <c r="F4" s="4">
+        <v>95.92027659141758</v>
+      </c>
+      <c r="G4" s="5">
+        <v>231</v>
+      </c>
+      <c r="H4" s="5">
+        <v>227</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>4</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>4</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.09332190511304479</v>
+      </c>
+      <c r="O4" s="5">
+        <v>231</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1389719619344004</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.0957310147496046</v>
+      </c>
+      <c r="R4" s="5">
+        <v>227</v>
+      </c>
+      <c r="S4" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.4465892586557714</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.4465892586557714</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.4986109320244747</v>
+      </c>
+      <c r="E5" s="4">
+        <v>85.92903828197949</v>
+      </c>
+      <c r="F5" s="4">
+        <v>86.97942711760336</v>
+      </c>
+      <c r="G5" s="5">
+        <v>153</v>
+      </c>
+      <c r="H5" s="5">
+        <v>153</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.4321987437689803</v>
+      </c>
+      <c r="O5" s="5">
+        <v>153</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.06626411792007679</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.06626411792007679</v>
+      </c>
+      <c r="R5" s="5">
+        <v>153</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.5994155994910354</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.6017700859195292</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.6140926581892613</v>
+      </c>
+      <c r="E3" s="4">
+        <v>91.37660927563221</v>
+      </c>
+      <c r="F3" s="4">
+        <v>93.27798788885781</v>
+      </c>
+      <c r="G3" s="5">
+        <v>307</v>
+      </c>
+      <c r="H3" s="5">
+        <v>303</v>
+      </c>
+      <c r="I3" s="5">
+        <v>4</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.5823196196068612</v>
+      </c>
+      <c r="O3" s="5">
+        <v>303</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1770103398802294</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1772183131185924</v>
+      </c>
+      <c r="R3" s="5">
+        <v>303</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.2138191976706706</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1734903253382384</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2163257650223993</v>
+      </c>
+      <c r="E4" s="4">
+        <v>93.34172630090997</v>
+      </c>
+      <c r="F4" s="4">
+        <v>95.36568949320622</v>
+      </c>
+      <c r="G4" s="5">
+        <v>231</v>
+      </c>
+      <c r="H4" s="5">
+        <v>226</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>4</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>4</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.08913460348938886</v>
+      </c>
+      <c r="O4" s="5">
+        <v>230</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1380690090288192</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09480116101348371</v>
+      </c>
+      <c r="R4" s="5">
+        <v>226</v>
+      </c>
+      <c r="S4" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.482407895186189</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.4863407523760505</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.5158941452617216</v>
+      </c>
+      <c r="E5" s="4">
+        <v>87.52701080432179</v>
+      </c>
+      <c r="F5" s="4">
+        <v>88.44350864879891</v>
+      </c>
+      <c r="G5" s="5">
+        <v>153</v>
+      </c>
+      <c r="H5" s="5">
+        <v>149</v>
+      </c>
+      <c r="I5" s="5">
+        <v>4</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.4721145678160595</v>
+      </c>
+      <c r="O5" s="5">
+        <v>149</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.07981589772527935</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.07716395305102233</v>
+      </c>
+      <c r="R5" s="5">
+        <v>149</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.6812169806394905</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.6824208972558082</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.6787180926773367</v>
+      </c>
+      <c r="E3" s="4">
+        <v>96.27595193921726</v>
+      </c>
+      <c r="F3" s="4">
+        <v>93.85611871350103</v>
+      </c>
+      <c r="G3" s="5">
+        <v>308</v>
+      </c>
+      <c r="H3" s="5">
+        <v>306</v>
+      </c>
+      <c r="I3" s="5">
+        <v>2</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.6674455712728179</v>
+      </c>
+      <c r="O3" s="5">
+        <v>306</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1552214953599204</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1551221075326654</v>
+      </c>
+      <c r="R3" s="5">
+        <v>306</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.1890525060844812</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1483792988537726</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.1909225951584987</v>
+      </c>
+      <c r="E4" s="4">
+        <v>97.24093947923996</v>
+      </c>
+      <c r="F4" s="4">
+        <v>95.23533325619118</v>
+      </c>
+      <c r="G4" s="5">
+        <v>232</v>
+      </c>
+      <c r="H4" s="5">
+        <v>227</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>5</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5">
+        <v>4</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.06266496222840873</v>
+      </c>
+      <c r="O4" s="5">
+        <v>231</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1363698945924287</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.0931559919053223</v>
+      </c>
+      <c r="R4" s="5">
+        <v>227</v>
+      </c>
+      <c r="S4" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.3803167717633587</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.382247133796072</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.4390526749774445</v>
+      </c>
+      <c r="E5" s="4">
+        <v>91.66843360720914</v>
+      </c>
+      <c r="F5" s="4">
+        <v>86.33661640373036</v>
+      </c>
+      <c r="G5" s="5">
+        <v>154</v>
+      </c>
+      <c r="H5" s="5">
+        <v>151</v>
+      </c>
+      <c r="I5" s="5">
+        <v>3</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.3665682988823945</v>
+      </c>
+      <c r="O5" s="5">
+        <v>151</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.07232712657493043</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.07082605666272372</v>
+      </c>
+      <c r="R5" s="5">
+        <v>151</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N23"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3956,7 +7806,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
         <v>1</v>
@@ -4861,9 +8711,1028 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N23"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>650</v>
+      </c>
+      <c r="C3" s="5">
+        <v>38</v>
+      </c>
+      <c r="D3" s="5">
+        <v>6</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5">
+        <v>1</v>
+      </c>
+      <c r="G3" s="5">
+        <v>4</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>638</v>
+      </c>
+      <c r="C4" s="5">
+        <v>50</v>
+      </c>
+      <c r="D4" s="5">
+        <v>6</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>2</v>
+      </c>
+      <c r="G4" s="5">
+        <v>4</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>2</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>475</v>
+      </c>
+      <c r="C5" s="5">
+        <v>211</v>
+      </c>
+      <c r="D5" s="5">
+        <v>8</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>4</v>
+      </c>
+      <c r="G5" s="5">
+        <v>4</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>4</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>685</v>
+      </c>
+      <c r="C6" s="5">
+        <v>2</v>
+      </c>
+      <c r="D6" s="5">
+        <v>4</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>4</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>509</v>
+      </c>
+      <c r="C7" s="5">
+        <v>162</v>
+      </c>
+      <c r="D7" s="5">
+        <v>20</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>16</v>
+      </c>
+      <c r="G7" s="5">
+        <v>4</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>16</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>688</v>
+      </c>
+      <c r="C8" s="5">
+        <v>2</v>
+      </c>
+      <c r="D8" s="5">
+        <v>4</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>4</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>679</v>
+      </c>
+      <c r="C9" s="5">
+        <v>8</v>
+      </c>
+      <c r="D9" s="5">
+        <v>4</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>4</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>645</v>
+      </c>
+      <c r="C10" s="5">
+        <v>45</v>
+      </c>
+      <c r="D10" s="5">
+        <v>4</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>4</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>666</v>
+      </c>
+      <c r="C11" s="5">
+        <v>24</v>
+      </c>
+      <c r="D11" s="5">
+        <v>4</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>4</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>664</v>
+      </c>
+      <c r="C12" s="5">
+        <v>24</v>
+      </c>
+      <c r="D12" s="5">
+        <v>6</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>2</v>
+      </c>
+      <c r="G12" s="5">
+        <v>4</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>2</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>670</v>
+      </c>
+      <c r="C13" s="5">
+        <v>20</v>
+      </c>
+      <c r="D13" s="5">
+        <v>4</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>4</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>599</v>
+      </c>
+      <c r="C14" s="5">
+        <v>91</v>
+      </c>
+      <c r="D14" s="5">
+        <v>4</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>4</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>682</v>
+      </c>
+      <c r="C15" s="5">
+        <v>8</v>
+      </c>
+      <c r="D15" s="5">
+        <v>4</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>4</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>676</v>
+      </c>
+      <c r="C16" s="5">
+        <v>14</v>
+      </c>
+      <c r="D16" s="5">
+        <v>4</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>4</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>479</v>
+      </c>
+      <c r="C17" s="5">
+        <v>211</v>
+      </c>
+      <c r="D17" s="5">
+        <v>4</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>4</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="25" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="5">
+        <v>675</v>
+      </c>
+      <c r="C18" s="5">
+        <v>14</v>
+      </c>
+      <c r="D18" s="5">
+        <v>5</v>
+      </c>
+      <c r="E18" s="5">
+        <v>1</v>
+      </c>
+      <c r="F18" s="5">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5">
+        <v>4</v>
+      </c>
+      <c r="H18" s="5">
+        <v>1</v>
+      </c>
+      <c r="I18" s="5">
+        <v>1</v>
+      </c>
+      <c r="J18" s="5">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5">
+        <v>0</v>
+      </c>
+      <c r="L18" s="5">
+        <v>0</v>
+      </c>
+      <c r="M18" s="5">
+        <v>0</v>
+      </c>
+      <c r="N18" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="25" customHeight="1">
+      <c r="A19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="5">
+        <v>651</v>
+      </c>
+      <c r="C19" s="5">
+        <v>38</v>
+      </c>
+      <c r="D19" s="5">
+        <v>5</v>
+      </c>
+      <c r="E19" s="5">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5">
+        <v>1</v>
+      </c>
+      <c r="G19" s="5">
+        <v>4</v>
+      </c>
+      <c r="H19" s="5">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5">
+        <v>0</v>
+      </c>
+      <c r="J19" s="5">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5">
+        <v>0</v>
+      </c>
+      <c r="L19" s="5">
+        <v>1</v>
+      </c>
+      <c r="M19" s="5">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="25" customHeight="1">
+      <c r="A20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="5">
+        <v>669</v>
+      </c>
+      <c r="C20" s="5">
+        <v>21</v>
+      </c>
+      <c r="D20" s="5">
+        <v>4</v>
+      </c>
+      <c r="E20" s="5">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5">
+        <v>4</v>
+      </c>
+      <c r="H20" s="5">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5">
+        <v>0</v>
+      </c>
+      <c r="J20" s="5">
+        <v>0</v>
+      </c>
+      <c r="K20" s="5">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5">
+        <v>0</v>
+      </c>
+      <c r="M20" s="5">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="25" customHeight="1">
+      <c r="A21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="5">
+        <v>686</v>
+      </c>
+      <c r="C21" s="5">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5">
+        <v>4</v>
+      </c>
+      <c r="E21" s="5">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5">
+        <v>4</v>
+      </c>
+      <c r="H21" s="5">
+        <v>0</v>
+      </c>
+      <c r="I21" s="5">
+        <v>0</v>
+      </c>
+      <c r="J21" s="5">
+        <v>0</v>
+      </c>
+      <c r="K21" s="5">
+        <v>0</v>
+      </c>
+      <c r="L21" s="5">
+        <v>0</v>
+      </c>
+      <c r="M21" s="5">
+        <v>0</v>
+      </c>
+      <c r="N21" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="25" customHeight="1">
+      <c r="A22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="5">
+        <v>678</v>
+      </c>
+      <c r="C22" s="5">
+        <v>9</v>
+      </c>
+      <c r="D22" s="5">
+        <v>4</v>
+      </c>
+      <c r="E22" s="5">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5">
+        <v>4</v>
+      </c>
+      <c r="H22" s="5">
+        <v>0</v>
+      </c>
+      <c r="I22" s="5">
+        <v>0</v>
+      </c>
+      <c r="J22" s="5">
+        <v>0</v>
+      </c>
+      <c r="K22" s="5">
+        <v>0</v>
+      </c>
+      <c r="L22" s="5">
+        <v>0</v>
+      </c>
+      <c r="M22" s="5">
+        <v>0</v>
+      </c>
+      <c r="N22" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="25" customHeight="1">
+      <c r="A23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="5">
+        <v>684</v>
+      </c>
+      <c r="C23" s="5">
+        <v>5</v>
+      </c>
+      <c r="D23" s="5">
+        <v>5</v>
+      </c>
+      <c r="E23" s="5">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5">
+        <v>1</v>
+      </c>
+      <c r="G23" s="5">
+        <v>4</v>
+      </c>
+      <c r="H23" s="5">
+        <v>0</v>
+      </c>
+      <c r="I23" s="5">
+        <v>0</v>
+      </c>
+      <c r="J23" s="5">
+        <v>0</v>
+      </c>
+      <c r="K23" s="5">
+        <v>0</v>
+      </c>
+      <c r="L23" s="5">
+        <v>1</v>
+      </c>
+      <c r="M23" s="5">
+        <v>0</v>
+      </c>
+      <c r="N23" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4874,9 +9743,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
@@ -4910,8 +9785,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4933,81 +9816,117 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3016267141979416</v>
+        <v>0.2502606488004695</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3090756370152416</v>
+        <v>0.2497650164429723</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3341605661492484</v>
+        <v>0.2421133608468519</v>
       </c>
       <c r="E3" s="4">
-        <v>99.32083222899551</v>
+        <v>93.86838501634352</v>
       </c>
       <c r="F3" s="4">
-        <v>96.84117057439258</v>
+        <v>93.79713966123425</v>
       </c>
       <c r="G3" s="5">
         <v>308</v>
       </c>
       <c r="H3" s="5">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="I3" s="5">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.06518891021182366</v>
+      </c>
+      <c r="O3" s="5">
+        <v>271</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2414794305780882</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2362093367003619</v>
+      </c>
+      <c r="R3" s="5">
+        <v>271</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1267023664415422</v>
+        <v>0.3009639911785603</v>
       </c>
       <c r="C4" s="4">
-        <v>0.0824079300066542</v>
+        <v>0.2534667016328755</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1297698425278807</v>
+        <v>0.2957686393558593</v>
       </c>
       <c r="E4" s="4">
-        <v>99.95073891625616</v>
+        <v>95.5075650950035</v>
       </c>
       <c r="F4" s="4">
-        <v>99.07096158296689</v>
+        <v>96.66333989045793</v>
       </c>
       <c r="G4" s="5">
         <v>232</v>
       </c>
       <c r="H4" s="5">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
         <v>0</v>
@@ -5015,50 +9934,86 @@
       <c r="M4" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2983983303771915</v>
+      </c>
+      <c r="O4" s="5">
+        <v>229</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1400471417350625</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09682705381842611</v>
+      </c>
+      <c r="R4" s="5">
+        <v>225</v>
+      </c>
+      <c r="S4" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B5" s="4">
-        <v>0.12749929934742</v>
+        <v>0.3956411254993838</v>
       </c>
       <c r="C5" s="4">
-        <v>0.12749929934742</v>
+        <v>0.3848393641806511</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1528067144097058</v>
+        <v>0.3991006123446509</v>
       </c>
       <c r="E5" s="4">
-        <v>99.61900344553409</v>
+        <v>95.69772064670025</v>
       </c>
       <c r="F5" s="4">
-        <v>98.145137859903</v>
+        <v>96.73625032685429</v>
       </c>
       <c r="G5" s="5">
         <v>154</v>
       </c>
       <c r="H5" s="5">
+        <v>153</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.3934116322213624</v>
+      </c>
+      <c r="O5" s="5">
         <v>154</v>
       </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
+      <c r="P5" s="4">
+        <v>0.1130621956767872</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1130621956767872</v>
+      </c>
+      <c r="R5" s="5">
+        <v>154</v>
+      </c>
+      <c r="S5" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5069,14 +10024,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5087,9 +10043,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
@@ -5123,8 +10085,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5146,120 +10116,174 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B3" s="4">
-        <v>0.7128454672845418</v>
+        <v>0.2678854670541688</v>
       </c>
       <c r="C3" s="4">
-        <v>0.7136767709091462</v>
+        <v>0.2603134161376034</v>
       </c>
       <c r="D3" s="4">
-        <v>0.7232942864125901</v>
+        <v>0.2320775916442764</v>
       </c>
       <c r="E3" s="4">
-        <v>92.18008375988853</v>
+        <v>93.24034808728764</v>
       </c>
       <c r="F3" s="4">
-        <v>93.9202719541769</v>
+        <v>92.28017228855985</v>
       </c>
       <c r="G3" s="5">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H3" s="5">
-        <v>306</v>
+        <v>279</v>
       </c>
       <c r="I3" s="5">
+        <v>29</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.1561613302062876</v>
+      </c>
+      <c r="O3" s="5">
+        <v>279</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.246034675249204</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2450856861865292</v>
+      </c>
+      <c r="R3" s="5">
+        <v>279</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.2063446970150139</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1500287315873409</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.1968006212491129</v>
+      </c>
+      <c r="E4" s="4">
+        <v>95.52677105324888</v>
+      </c>
+      <c r="F4" s="4">
+        <v>93.30565841240491</v>
+      </c>
+      <c r="G4" s="5">
+        <v>232</v>
+      </c>
+      <c r="H4" s="5">
+        <v>207</v>
+      </c>
+      <c r="I4" s="5">
+        <v>19</v>
+      </c>
+      <c r="J4" s="5">
+        <v>6</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2</v>
+      </c>
+      <c r="M4" s="5">
+        <v>4</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.1821133838197395</v>
+      </c>
+      <c r="O4" s="5">
+        <v>211</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.159461458032523</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1157150819621666</v>
+      </c>
+      <c r="R4" s="5">
+        <v>207</v>
+      </c>
+      <c r="S4" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.3160375639076674</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.3074143248283744</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.3046561563697332</v>
+      </c>
+      <c r="E5" s="4">
+        <v>96.05928085519922</v>
+      </c>
+      <c r="F5" s="4">
+        <v>95.92354513495468</v>
+      </c>
+      <c r="G5" s="5">
+        <v>154</v>
+      </c>
+      <c r="H5" s="5">
+        <v>151</v>
+      </c>
+      <c r="I5" s="5">
+        <v>2</v>
+      </c>
+      <c r="J5" s="5">
         <v>1</v>
       </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.21800208731579</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.1777981803159182</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.2179079735064522</v>
-      </c>
-      <c r="E4" s="4">
-        <v>94.10857849633359</v>
-      </c>
-      <c r="F4" s="4">
-        <v>95.92027659141758</v>
-      </c>
-      <c r="G4" s="5">
-        <v>231</v>
-      </c>
-      <c r="H4" s="5">
-        <v>227</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>4</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.4465892586557714</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.4465892586557714</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.4986109320244747</v>
-      </c>
-      <c r="E5" s="4">
-        <v>85.92903828197949</v>
-      </c>
-      <c r="F5" s="4">
-        <v>86.97942711760336</v>
-      </c>
-      <c r="G5" s="5">
-        <v>153</v>
-      </c>
-      <c r="H5" s="5">
-        <v>153</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
@@ -5267,11 +10291,29 @@
         <v>0</v>
       </c>
       <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.2879505090378867</v>
+      </c>
+      <c r="O5" s="5">
+        <v>152</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1737474565787117</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1707147312694679</v>
+      </c>
+      <c r="R5" s="5">
+        <v>152</v>
+      </c>
+      <c r="S5" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5282,14 +10324,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5300,9 +10343,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
@@ -5336,8 +10385,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5359,119 +10416,173 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5994155994910354</v>
+        <v>0.5467273539928179</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6017700859195292</v>
+        <v>0.57852647678973</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6140926581892613</v>
+        <v>0.3087406124790759</v>
       </c>
       <c r="E3" s="4">
-        <v>91.37660927563221</v>
+        <v>85.61301793444605</v>
       </c>
       <c r="F3" s="4">
-        <v>93.27798788885781</v>
+        <v>79.75173595978973</v>
       </c>
       <c r="G3" s="5">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H3" s="5">
-        <v>303</v>
+        <v>101</v>
       </c>
       <c r="I3" s="5">
-        <v>4</v>
+        <v>204</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.5552791065275079</v>
+      </c>
+      <c r="O3" s="5">
+        <v>101</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2893908034884709</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3315576615430237</v>
+      </c>
+      <c r="R3" s="5">
+        <v>101</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2138191976706706</v>
+        <v>0.2226282787097803</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1734903253382384</v>
+        <v>0.1812430845727538</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2163257650223993</v>
+        <v>0.2586193972036426</v>
       </c>
       <c r="E4" s="4">
-        <v>93.34172630090997</v>
+        <v>95.28589021815621</v>
       </c>
       <c r="F4" s="4">
-        <v>95.36568949320622</v>
+        <v>94.30475198642235</v>
       </c>
       <c r="G4" s="5">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H4" s="5">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="I4" s="5">
+        <v>7</v>
+      </c>
+      <c r="J4" s="5">
+        <v>5</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
         <v>1</v>
       </c>
-      <c r="J4" s="5">
-        <v>4</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
       <c r="M4" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.04079672490408567</v>
+      </c>
+      <c r="O4" s="5">
+        <v>224</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2019003699061209</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1582719246096924</v>
+      </c>
+      <c r="R4" s="5">
+        <v>220</v>
+      </c>
+      <c r="S4" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B5" s="4">
-        <v>0.482407895186189</v>
+        <v>0.8199264452808004</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4863407523760505</v>
+        <v>0.8089323321333816</v>
       </c>
       <c r="D5" s="4">
-        <v>0.5158941452617216</v>
+        <v>0.7698682042664436</v>
       </c>
       <c r="E5" s="4">
-        <v>87.52701080432179</v>
+        <v>94.50636098595285</v>
       </c>
       <c r="F5" s="4">
-        <v>88.44350864879891</v>
+        <v>93.97796275313057</v>
       </c>
       <c r="G5" s="5">
+        <v>154</v>
+      </c>
+      <c r="H5" s="5">
         <v>153</v>
       </c>
-      <c r="H5" s="5">
-        <v>149</v>
-      </c>
       <c r="I5" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -5480,11 +10591,29 @@
         <v>0</v>
       </c>
       <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.8199264452808004</v>
+      </c>
+      <c r="O5" s="5">
+        <v>154</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1523299760084152</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1523299760084152</v>
+      </c>
+      <c r="R5" s="5">
+        <v>154</v>
+      </c>
+      <c r="S5" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5495,14 +10624,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5513,9 +10643,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
@@ -5549,8 +10685,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5572,31 +10716,49 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6812169806394905</v>
+        <v>0.2366539658174759</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6824208972558082</v>
+        <v>0.2364231717672533</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6787180926773367</v>
+        <v>0.1933261797506749</v>
       </c>
       <c r="E3" s="4">
-        <v>96.27595193921726</v>
+        <v>96.96813578851733</v>
       </c>
       <c r="F3" s="4">
-        <v>93.85611871350103</v>
+        <v>95.43733467415773</v>
       </c>
       <c r="G3" s="5">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H3" s="5">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I3" s="5">
         <v>2</v>
@@ -5613,28 +10775,46 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2107684384597833</v>
+      </c>
+      <c r="O3" s="5">
+        <v>305</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1445831666221289</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1451307177474108</v>
+      </c>
+      <c r="R3" s="5">
+        <v>305</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1890525060844812</v>
+        <v>0.112313052659207</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1483792988537726</v>
+        <v>0.06812098900549551</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1909225951584987</v>
+        <v>0.1140937000352671</v>
       </c>
       <c r="E4" s="4">
-        <v>97.24093947923996</v>
+        <v>98.61648555526104</v>
       </c>
       <c r="F4" s="4">
-        <v>95.23533325619118</v>
+        <v>97.42341923549955</v>
       </c>
       <c r="G4" s="5">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H4" s="5">
         <v>227</v>
@@ -5643,49 +10823,67 @@
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>4</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.05486562103821628</v>
+      </c>
+      <c r="O4" s="5">
+        <v>231</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1400700520416136</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09733389359355182</v>
+      </c>
+      <c r="R4" s="5">
+        <v>227</v>
+      </c>
+      <c r="S4" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.3467268672070843</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.3354481222980842</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.3310785214254135</v>
+      </c>
+      <c r="E5" s="4">
+        <v>97.97052154195015</v>
+      </c>
+      <c r="F5" s="4">
+        <v>97.33364039127964</v>
+      </c>
+      <c r="G5" s="5">
+        <v>153</v>
+      </c>
+      <c r="H5" s="5">
+        <v>152</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
         <v>1</v>
       </c>
-      <c r="M4" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.3803167717633587</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.382247133796072</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.4390526749774445</v>
-      </c>
-      <c r="E5" s="4">
-        <v>91.66843360720914</v>
-      </c>
-      <c r="F5" s="4">
-        <v>86.33661640373036</v>
-      </c>
-      <c r="G5" s="5">
-        <v>154</v>
-      </c>
-      <c r="H5" s="5">
-        <v>151</v>
-      </c>
-      <c r="I5" s="5">
-        <v>3</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
@@ -5693,11 +10891,29 @@
         <v>0</v>
       </c>
       <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.2886066455250434</v>
+      </c>
+      <c r="O5" s="5">
+        <v>153</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2012543914915975</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2012543914915975</v>
+      </c>
+      <c r="R5" s="5">
+        <v>153</v>
+      </c>
+      <c r="S5" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5708,14 +10924,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5726,9 +10943,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
@@ -5762,8 +10985,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5785,132 +11016,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2502606488004695</v>
+        <v>0.6704950673624134</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2497650164429723</v>
+        <v>0.5593193327142015</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2421133608468519</v>
+        <v>0.608981676519351</v>
       </c>
       <c r="E3" s="4">
-        <v>93.86838501634352</v>
+        <v>84.99678698841079</v>
       </c>
       <c r="F3" s="4">
-        <v>93.79713966123425</v>
+        <v>83.35887458190385</v>
       </c>
       <c r="G3" s="5">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H3" s="5">
-        <v>271</v>
+        <v>153</v>
       </c>
       <c r="I3" s="5">
-        <v>36</v>
+        <v>146</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.426705432864507</v>
+      </c>
+      <c r="O3" s="5">
+        <v>153</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6270532656210741</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3848309962227004</v>
+      </c>
+      <c r="R3" s="5">
+        <v>153</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3009639911785603</v>
+        <v>0.2756406540019677</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2534667016328755</v>
+        <v>0.1333078013483276</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2957686393558593</v>
+        <v>0.1928495683554549</v>
       </c>
       <c r="E4" s="4">
-        <v>95.5075650950035</v>
+        <v>91.9141855876553</v>
       </c>
       <c r="F4" s="4">
-        <v>96.66333989045793</v>
+        <v>92.20667848184748</v>
       </c>
       <c r="G4" s="5">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H4" s="5">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J4" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M4" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.03584356198858929</v>
+      </c>
+      <c r="O4" s="5">
+        <v>223</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2882418294013097</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1482361444402633</v>
+      </c>
+      <c r="R4" s="5">
+        <v>219</v>
+      </c>
+      <c r="S4" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3956411254993838</v>
+        <v>0.6478382985578072</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3848393641806511</v>
+        <v>0.4215640995115584</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3991006123446509</v>
+        <v>0.3720757207577562</v>
       </c>
       <c r="E5" s="4">
-        <v>95.69772064670025</v>
+        <v>89.05917922724747</v>
       </c>
       <c r="F5" s="4">
-        <v>96.73625032685429</v>
+        <v>88.87872673305202</v>
       </c>
       <c r="G5" s="5">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H5" s="5">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M5" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.4215640995115584</v>
+      </c>
+      <c r="O5" s="5">
+        <v>137</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3734327072429083</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1642828293476696</v>
+      </c>
+      <c r="R5" s="5">
+        <v>137</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5921,1284 +11224,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.2678854670541688</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.2603134161376034</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.2320775916442764</v>
-      </c>
-      <c r="E3" s="4">
-        <v>93.24034808728764</v>
-      </c>
-      <c r="F3" s="4">
-        <v>92.28017228855985</v>
-      </c>
-      <c r="G3" s="5">
-        <v>308</v>
-      </c>
-      <c r="H3" s="5">
-        <v>279</v>
-      </c>
-      <c r="I3" s="5">
-        <v>29</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.2063446970150139</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.1500287315873409</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.1968006212491129</v>
-      </c>
-      <c r="E4" s="4">
-        <v>95.52677105324888</v>
-      </c>
-      <c r="F4" s="4">
-        <v>93.30565841240491</v>
-      </c>
-      <c r="G4" s="5">
-        <v>232</v>
-      </c>
-      <c r="H4" s="5">
-        <v>207</v>
-      </c>
-      <c r="I4" s="5">
-        <v>19</v>
-      </c>
-      <c r="J4" s="5">
-        <v>6</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>2</v>
-      </c>
-      <c r="M4" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.3160375639076674</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.3074143248283744</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.3046561563697332</v>
-      </c>
-      <c r="E5" s="4">
-        <v>96.05928085519922</v>
-      </c>
-      <c r="F5" s="4">
-        <v>95.92354513495468</v>
-      </c>
-      <c r="G5" s="5">
-        <v>154</v>
-      </c>
-      <c r="H5" s="5">
-        <v>151</v>
-      </c>
-      <c r="I5" s="5">
-        <v>2</v>
-      </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.5467273539928179</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.57852647678973</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.3087406124790759</v>
-      </c>
-      <c r="E3" s="4">
-        <v>85.61301793444605</v>
-      </c>
-      <c r="F3" s="4">
-        <v>79.75173595978973</v>
-      </c>
-      <c r="G3" s="5">
-        <v>308</v>
-      </c>
-      <c r="H3" s="5">
-        <v>101</v>
-      </c>
-      <c r="I3" s="5">
-        <v>204</v>
-      </c>
-      <c r="J3" s="5">
-        <v>3</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>3</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.2226282787097803</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.1812430845727538</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.2586193972036426</v>
-      </c>
-      <c r="E4" s="4">
-        <v>95.28589021815621</v>
-      </c>
-      <c r="F4" s="4">
-        <v>94.30475198642235</v>
-      </c>
-      <c r="G4" s="5">
-        <v>232</v>
-      </c>
-      <c r="H4" s="5">
-        <v>220</v>
-      </c>
-      <c r="I4" s="5">
-        <v>7</v>
-      </c>
-      <c r="J4" s="5">
-        <v>5</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.8199264452808004</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.8089323321333816</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.7698682042664436</v>
-      </c>
-      <c r="E5" s="4">
-        <v>94.50636098595285</v>
-      </c>
-      <c r="F5" s="4">
-        <v>93.97796275313057</v>
-      </c>
-      <c r="G5" s="5">
-        <v>154</v>
-      </c>
-      <c r="H5" s="5">
-        <v>153</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.2366539658174759</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.2364231717672533</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.1933261797506749</v>
-      </c>
-      <c r="E3" s="4">
-        <v>96.96813578851733</v>
-      </c>
-      <c r="F3" s="4">
-        <v>95.43733467415773</v>
-      </c>
-      <c r="G3" s="5">
-        <v>307</v>
-      </c>
-      <c r="H3" s="5">
-        <v>305</v>
-      </c>
-      <c r="I3" s="5">
-        <v>2</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.112313052659207</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.06812098900549551</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.1140937000352671</v>
-      </c>
-      <c r="E4" s="4">
-        <v>98.61648555526104</v>
-      </c>
-      <c r="F4" s="4">
-        <v>97.42341923549955</v>
-      </c>
-      <c r="G4" s="5">
-        <v>231</v>
-      </c>
-      <c r="H4" s="5">
-        <v>227</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>4</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.3467268672070843</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.3354481222980842</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.3310785214254135</v>
-      </c>
-      <c r="E5" s="4">
-        <v>97.97052154195015</v>
-      </c>
-      <c r="F5" s="4">
-        <v>97.33364039127964</v>
-      </c>
-      <c r="G5" s="5">
-        <v>153</v>
-      </c>
-      <c r="H5" s="5">
-        <v>152</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.6704950673624134</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.5593193327142015</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.608981676519351</v>
-      </c>
-      <c r="E3" s="4">
-        <v>84.99678698841079</v>
-      </c>
-      <c r="F3" s="4">
-        <v>83.35887458190385</v>
-      </c>
-      <c r="G3" s="5">
-        <v>307</v>
-      </c>
-      <c r="H3" s="5">
-        <v>153</v>
-      </c>
-      <c r="I3" s="5">
-        <v>146</v>
-      </c>
-      <c r="J3" s="5">
-        <v>8</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>8</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.2756406540019677</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.1333078013483276</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.1928495683554549</v>
-      </c>
-      <c r="E4" s="4">
-        <v>91.9141855876553</v>
-      </c>
-      <c r="F4" s="4">
-        <v>92.20667848184748</v>
-      </c>
-      <c r="G4" s="5">
-        <v>231</v>
-      </c>
-      <c r="H4" s="5">
-        <v>219</v>
-      </c>
-      <c r="I4" s="5">
-        <v>4</v>
-      </c>
-      <c r="J4" s="5">
-        <v>8</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>4</v>
-      </c>
-      <c r="M4" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.6478382985578072</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.4215640995115584</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.3720757207577562</v>
-      </c>
-      <c r="E5" s="4">
-        <v>89.05917922724747</v>
-      </c>
-      <c r="F5" s="4">
-        <v>88.87872673305202</v>
-      </c>
-      <c r="G5" s="5">
-        <v>153</v>
-      </c>
-      <c r="H5" s="5">
-        <v>137</v>
-      </c>
-      <c r="I5" s="5">
-        <v>12</v>
-      </c>
-      <c r="J5" s="5">
-        <v>4</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>4</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.1747231270581385</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.1730039562296326</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.1772082199728205</v>
-      </c>
-      <c r="E3" s="4">
-        <v>98.65756692287309</v>
-      </c>
-      <c r="F3" s="4">
-        <v>98.44998402045353</v>
-      </c>
-      <c r="G3" s="5">
-        <v>308</v>
-      </c>
-      <c r="H3" s="5">
-        <v>306</v>
-      </c>
-      <c r="I3" s="5">
-        <v>2</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.09178078059807288</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.04725108086251267</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.09178245260472866</v>
-      </c>
-      <c r="E4" s="4">
-        <v>98.74868050668539</v>
-      </c>
-      <c r="F4" s="4">
-        <v>98.82680513769948</v>
-      </c>
-      <c r="G4" s="5">
-        <v>232</v>
-      </c>
-      <c r="H4" s="5">
-        <v>228</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>4</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.05665666167141403</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.05665666167141403</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.06358868097321044</v>
-      </c>
-      <c r="E5" s="4">
-        <v>98.80753600141355</v>
-      </c>
-      <c r="F5" s="4">
-        <v>98.64268282053519</v>
-      </c>
-      <c r="G5" s="5">
-        <v>154</v>
-      </c>
-      <c r="H5" s="5">
-        <v>154</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.6818642686801094</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.689000376986189</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.478326652566046</v>
-      </c>
-      <c r="E3" s="4">
-        <v>93.04826164993702</v>
-      </c>
-      <c r="F3" s="4">
-        <v>90.51002339155767</v>
-      </c>
-      <c r="G3" s="5">
-        <v>307</v>
-      </c>
-      <c r="H3" s="5">
-        <v>299</v>
-      </c>
-      <c r="I3" s="5">
-        <v>8</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.1070954113478725</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.06243687450106532</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.1062151984660457</v>
-      </c>
-      <c r="E4" s="4">
-        <v>97.94107253290926</v>
-      </c>
-      <c r="F4" s="4">
-        <v>97.332287399401</v>
-      </c>
-      <c r="G4" s="5">
-        <v>231</v>
-      </c>
-      <c r="H4" s="5">
-        <v>227</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>4</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.7234713694326804</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.711974522225548</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.6363215259329524</v>
-      </c>
-      <c r="E5" s="4">
-        <v>93.86021075096713</v>
-      </c>
-      <c r="F5" s="4">
-        <v>91.36048602886363</v>
-      </c>
-      <c r="G5" s="5">
-        <v>153</v>
-      </c>
-      <c r="H5" s="5">
-        <v>152</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/KHLOHC.xlsx
+++ b/public/downloads/KHLOHC.xlsx
@@ -1881,16 +1881,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1037121084844398</v>
+        <v>0.1710656132938766</v>
       </c>
       <c r="O3" s="5">
         <v>306</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1398895541236778</v>
+        <v>0.1317807003856285</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1372648559656365</v>
+        <v>0.1286627841978651</v>
       </c>
       <c r="R3" s="5">
         <v>306</v>
@@ -1940,16 +1940,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.05765184590726619</v>
+        <v>0.002048201022826213</v>
       </c>
       <c r="O4" s="5">
         <v>232</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1227985124646461</v>
+        <v>0.09176137213646372</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.07982441935669711</v>
+        <v>0.04719539855029939</v>
       </c>
       <c r="R4" s="5">
         <v>228</v>
@@ -1999,16 +1999,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.01754591749840116</v>
+        <v>0.03713414901597645</v>
       </c>
       <c r="O5" s="5">
         <v>154</v>
       </c>
       <c r="P5" s="4">
-        <v>0.04951980356588364</v>
+        <v>0.0460622778943604</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.04951980356588364</v>
+        <v>0.0460622778943604</v>
       </c>
       <c r="R5" s="5">
         <v>154</v>
@@ -2181,16 +2181,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.689000376986189</v>
+        <v>-0.6697067737227229</v>
       </c>
       <c r="O3" s="5">
         <v>299</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1522358564051578</v>
+        <v>0.1505332028141503</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1476393081384311</v>
+        <v>0.146278261205794</v>
       </c>
       <c r="R3" s="5">
         <v>299</v>
@@ -2240,16 +2240,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.07817627081378893</v>
+        <v>-0.01426564793743124</v>
       </c>
       <c r="O4" s="5">
         <v>231</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1309277763447348</v>
+        <v>0.1054153893348855</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.08806674849899634</v>
+        <v>0.06097862563212145</v>
       </c>
       <c r="R4" s="5">
         <v>227</v>
@@ -2299,16 +2299,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.7234713694326804</v>
+        <v>-0.7698588561068505</v>
       </c>
       <c r="O5" s="5">
         <v>153</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1964927696729257</v>
+        <v>0.194844764440793</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1964927696729257</v>
+        <v>0.194844764440793</v>
       </c>
       <c r="R5" s="5">
         <v>153</v>
@@ -2481,16 +2481,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.853089881921901</v>
+        <v>0.9189546535829578</v>
       </c>
       <c r="O3" s="5">
         <v>276</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2405115577537076</v>
+        <v>0.2399662683846711</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2270938416167456</v>
+        <v>0.21980339693496</v>
       </c>
       <c r="R3" s="5">
         <v>276</v>
@@ -2540,16 +2540,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>0.09205577406635082</v>
+        <v>0.1761771023296275</v>
       </c>
       <c r="O4" s="5">
         <v>232</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1598206293975123</v>
+        <v>0.1333403061057145</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1174353317568217</v>
+        <v>0.08901462861318048</v>
       </c>
       <c r="R4" s="5">
         <v>228</v>
@@ -2599,16 +2599,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2929196370526368</v>
+        <v>0.3096791115460462</v>
       </c>
       <c r="O5" s="5">
         <v>141</v>
       </c>
       <c r="P5" s="4">
-        <v>0.06167278742775525</v>
+        <v>0.05831793794110524</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.06145314372164591</v>
+        <v>0.05799902131582943</v>
       </c>
       <c r="R5" s="5">
         <v>141</v>
@@ -2781,16 +2781,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2431503031821704</v>
+        <v>0.2657056859674327</v>
       </c>
       <c r="O3" s="5">
         <v>284</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1609080366587531</v>
+        <v>0.1602402804847319</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1532612936761197</v>
+        <v>0.1517352792709364</v>
       </c>
       <c r="R3" s="5">
         <v>284</v>
@@ -2840,16 +2840,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>0.004954208121248896</v>
+        <v>0.07733601859337114</v>
       </c>
       <c r="O4" s="5">
         <v>232</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1405788965578048</v>
+        <v>0.1197131890461824</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.09775611087875714</v>
+        <v>0.07525448199899892</v>
       </c>
       <c r="R4" s="5">
         <v>228</v>
@@ -2899,16 +2899,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.04693473124373062</v>
+        <v>-0.05509342394434213</v>
       </c>
       <c r="O5" s="5">
         <v>154</v>
       </c>
       <c r="P5" s="4">
-        <v>0.07005391271023895</v>
+        <v>0.06954540307935025</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.07005391271023895</v>
+        <v>0.06954540307935025</v>
       </c>
       <c r="R5" s="5">
         <v>154</v>
@@ -3081,16 +3081,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.8387115364509898</v>
+        <v>-0.8498817430357661</v>
       </c>
       <c r="O3" s="5">
         <v>288</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2334522486689607</v>
+        <v>0.2332072265408491</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2338872204890554</v>
+        <v>0.2334700411772587</v>
       </c>
       <c r="R3" s="5">
         <v>288</v>
@@ -3140,16 +3140,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2373419884960072</v>
+        <v>-0.2026152332749276</v>
       </c>
       <c r="O4" s="5">
         <v>227</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1508116504948084</v>
+        <v>0.1479920730281801</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1049815757642049</v>
+        <v>0.1009581261731496</v>
       </c>
       <c r="R4" s="5">
         <v>223</v>
@@ -3199,16 +3199,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.9943860155639669</v>
+        <v>-1.093465359331034</v>
       </c>
       <c r="O5" s="5">
         <v>153</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2272079529865117</v>
+        <v>0.2149850659697102</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2242271631713107</v>
+        <v>0.2112768105938303</v>
       </c>
       <c r="R5" s="5">
         <v>153</v>
@@ -3381,16 +3381,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2022987911914177</v>
+        <v>0.3109881154623082</v>
       </c>
       <c r="O3" s="5">
         <v>295</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2068722594079844</v>
+        <v>0.1950412052077058</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.205586147650668</v>
+        <v>0.1902264036711053</v>
       </c>
       <c r="R3" s="5">
         <v>295</v>
@@ -3440,16 +3440,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>0.02467098531829064</v>
+        <v>0.1074705099679831</v>
       </c>
       <c r="O4" s="5">
         <v>225</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1558554010642385</v>
+        <v>0.1366586699271602</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1145141063014864</v>
+        <v>0.09024063845103943</v>
       </c>
       <c r="R4" s="5">
         <v>221</v>
@@ -3499,16 +3499,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1964945202325618</v>
+        <v>0.2111518627692419</v>
       </c>
       <c r="O5" s="5">
         <v>154</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1743372584373704</v>
+        <v>0.1740842401624004</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1743372584373704</v>
+        <v>0.1740842401624004</v>
       </c>
       <c r="R5" s="5">
         <v>154</v>
@@ -3681,16 +3681,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.0181111939903482</v>
+        <v>-0.04554884245070667</v>
       </c>
       <c r="O3" s="5">
         <v>226</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2680748283878875</v>
+        <v>0.265189516782597</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2651761754744615</v>
+        <v>0.2641088363532759</v>
       </c>
       <c r="R3" s="5">
         <v>226</v>
@@ -3740,16 +3740,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2789129502726771</v>
+        <v>-0.2097113247550078</v>
       </c>
       <c r="O4" s="5">
         <v>225</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1997622601065639</v>
+        <v>0.1893617174961482</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1558017825781094</v>
+        <v>0.1420654001560485</v>
       </c>
       <c r="R4" s="5">
         <v>221</v>
@@ -3799,16 +3799,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>-1.340250262819442</v>
+        <v>-1.454825731540808</v>
       </c>
       <c r="O5" s="5">
         <v>152</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2728727075613891</v>
+        <v>0.2664451698358844</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.275244678369006</v>
+        <v>0.2676801888954237</v>
       </c>
       <c r="R5" s="5">
         <v>152</v>
@@ -3981,16 +3981,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2558399698652549</v>
+        <v>-0.214867454610058</v>
       </c>
       <c r="O3" s="5">
         <v>301</v>
       </c>
       <c r="P3" s="4">
-        <v>0.13580061670645</v>
+        <v>0.1321684655159831</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1362613564187887</v>
+        <v>0.1315918874040041</v>
       </c>
       <c r="R3" s="5">
         <v>301</v>
@@ -4040,16 +4040,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.106286276991591</v>
+        <v>-0.03374722379495676</v>
       </c>
       <c r="O4" s="5">
         <v>231</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1353074557006402</v>
+        <v>0.1138818172728455</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.09301605303189653</v>
+        <v>0.06952070774012767</v>
       </c>
       <c r="R4" s="5">
         <v>227</v>
@@ -4099,16 +4099,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2780137343733411</v>
+        <v>-0.2734164514523343</v>
       </c>
       <c r="O5" s="5">
         <v>154</v>
       </c>
       <c r="P5" s="4">
-        <v>0.06350181927233636</v>
+        <v>0.0632475531793722</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.06350181927233636</v>
+        <v>0.0632475531793722</v>
       </c>
       <c r="R5" s="5">
         <v>154</v>
@@ -4281,16 +4281,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1630816105324231</v>
+        <v>-0.07902402215486859</v>
       </c>
       <c r="O3" s="5">
         <v>294</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2449112875908699</v>
+        <v>0.2364036995328934</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2368105660439171</v>
+        <v>0.2238951124413916</v>
       </c>
       <c r="R3" s="5">
         <v>294</v>
@@ -4340,16 +4340,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1139141107467376</v>
+        <v>-0.04248907734517315</v>
       </c>
       <c r="O4" s="5">
         <v>232</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1312249869931747</v>
+        <v>0.1037350224818606</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.08881018313892969</v>
+        <v>0.05958486778703886</v>
       </c>
       <c r="R4" s="5">
         <v>228</v>
@@ -4399,16 +4399,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.007278023348592282</v>
+        <v>0.03307268264015306</v>
       </c>
       <c r="O5" s="5">
         <v>154</v>
       </c>
       <c r="P5" s="4">
-        <v>0.08152644095140034</v>
+        <v>0.07282785170151453</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.08152644095140034</v>
+        <v>0.07282785170151453</v>
       </c>
       <c r="R5" s="5">
         <v>154</v>
@@ -4581,16 +4581,16 @@
         <v>122</v>
       </c>
       <c r="N3" s="4">
-        <v>-2.176216331691623</v>
+        <v>-2.197018538830704</v>
       </c>
       <c r="O3" s="5">
         <v>151</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2321551062586826</v>
+        <v>0.238800408765089</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1648517515010344</v>
+        <v>0.1640491398344765</v>
       </c>
       <c r="R3" s="5">
         <v>151</v>
@@ -4640,16 +4640,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>0.09895913131356285</v>
+        <v>0.1784706855445064</v>
       </c>
       <c r="O4" s="5">
         <v>225</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2070214907310166</v>
+        <v>0.1871123005272579</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1641380610247808</v>
+        <v>0.1410900348186074</v>
       </c>
       <c r="R4" s="5">
         <v>221</v>
@@ -4699,16 +4699,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>-1.391895791187406</v>
+        <v>-1.49649743552213</v>
       </c>
       <c r="O5" s="5">
         <v>107</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2879128843864758</v>
+        <v>0.2610601069567939</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2911453713384908</v>
+        <v>0.2855779625571513</v>
       </c>
       <c r="R5" s="5">
         <v>107</v>
@@ -4845,13 +4845,13 @@
         <v>0.5763688760806917</v>
       </c>
       <c r="H3" s="4">
-        <v>0.1790751867936757</v>
+        <v>0.1683635136419022</v>
       </c>
       <c r="I3" s="4">
-        <v>0.158785223829491</v>
+        <v>0.1424688567538166</v>
       </c>
       <c r="J3" s="4">
-        <v>0.1721234791840562</v>
+        <v>0.1564379527773931</v>
       </c>
       <c r="K3" s="4">
         <v>94.82228626320787</v>
@@ -4895,13 +4895,13 @@
         <v>0.5763688760806917</v>
       </c>
       <c r="H4" s="4">
-        <v>0.2010530930164579</v>
+        <v>0.1984120678286427</v>
       </c>
       <c r="I4" s="4">
-        <v>0.1853927391303593</v>
+        <v>0.1807702898119162</v>
       </c>
       <c r="J4" s="4">
-        <v>0.2141635307746295</v>
+        <v>0.2059101402504845</v>
       </c>
       <c r="K4" s="4">
         <v>94.63021231547464</v>
@@ -4945,13 +4945,13 @@
         <v>0.5763688760806917</v>
       </c>
       <c r="H5" s="4">
-        <v>0.2297292069134943</v>
+        <v>0.2212418890609525</v>
       </c>
       <c r="I5" s="4">
-        <v>0.1931915021795235</v>
+        <v>0.1750195025544801</v>
       </c>
       <c r="J5" s="4">
-        <v>0.3248375495630413</v>
+        <v>0.2916526768717883</v>
       </c>
       <c r="K5" s="4">
         <v>90.82005136348444</v>
@@ -4995,13 +4995,13 @@
         <v>0.5788712011577424</v>
       </c>
       <c r="H6" s="4">
-        <v>0.1556224834628375</v>
+        <v>0.1416603138537441</v>
       </c>
       <c r="I6" s="4">
-        <v>0.1418271308860014</v>
+        <v>0.1272777000967469</v>
       </c>
       <c r="J6" s="4">
-        <v>0.1608892537850728</v>
+        <v>0.1432995499121105</v>
       </c>
       <c r="K6" s="4">
         <v>97.74112249820332</v>
@@ -5045,13 +5045,13 @@
         <v>0.5788712011577424</v>
       </c>
       <c r="H7" s="4">
-        <v>0.457633023654902</v>
+        <v>0.480632539886499</v>
       </c>
       <c r="I7" s="4">
-        <v>0.2236730956289225</v>
+        <v>0.1972534913194381</v>
       </c>
       <c r="J7" s="4">
-        <v>0.3028114932141261</v>
+        <v>0.2794656629308621</v>
       </c>
       <c r="K7" s="4">
         <v>88.20874804335618</v>
@@ -5095,13 +5095,13 @@
         <v>0.5763688760806917</v>
       </c>
       <c r="H8" s="4">
-        <v>0.1141228923790154</v>
+        <v>0.09938139027401248</v>
       </c>
       <c r="I8" s="4">
-        <v>0.0985887547790084</v>
+        <v>0.08317580469439895</v>
       </c>
       <c r="J8" s="4">
-        <v>0.1141869109013268</v>
+        <v>0.09740546949332186</v>
       </c>
       <c r="K8" s="4">
         <v>98.72130408359311</v>
@@ -5145,13 +5145,13 @@
         <v>0.5788712011577424</v>
       </c>
       <c r="H9" s="4">
-        <v>0.1549118929261575</v>
+        <v>0.1452617903903677</v>
       </c>
       <c r="I9" s="4">
-        <v>0.1387315151732263</v>
+        <v>0.1287048557856632</v>
       </c>
       <c r="J9" s="4">
-        <v>0.2026670140428191</v>
+        <v>0.1870068961864535</v>
       </c>
       <c r="K9" s="4">
         <v>94.86369945952238</v>
@@ -5195,13 +5195,13 @@
         <v>0.5763688760806917</v>
       </c>
       <c r="H10" s="4">
-        <v>0.1738523848303158</v>
+        <v>0.1640137235186379</v>
       </c>
       <c r="I10" s="4">
-        <v>0.1521210064984949</v>
+        <v>0.1381998990440094</v>
       </c>
       <c r="J10" s="4">
-        <v>0.1787987858484355</v>
+        <v>0.1608164163421109</v>
       </c>
       <c r="K10" s="4">
         <v>93.88269717108743</v>
@@ -5245,13 +5245,13 @@
         <v>0.5763688760806917</v>
       </c>
       <c r="H11" s="4">
-        <v>0.1339514147689963</v>
+        <v>0.1265669428274231</v>
       </c>
       <c r="I11" s="4">
-        <v>0.115019374236864</v>
+        <v>0.1065477977221286</v>
       </c>
       <c r="J11" s="4">
-        <v>0.1402678547453275</v>
+        <v>0.1309666700822907</v>
       </c>
       <c r="K11" s="4">
         <v>99.14809151326234</v>
@@ -5295,13 +5295,13 @@
         <v>0.5763688760806917</v>
       </c>
       <c r="H12" s="4">
-        <v>0.2044403750212655</v>
+        <v>0.2006767822427301</v>
       </c>
       <c r="I12" s="4">
-        <v>0.1883692272010183</v>
+        <v>0.1838529909887333</v>
       </c>
       <c r="J12" s="4">
-        <v>0.2265662277804357</v>
+        <v>0.2461755941690831</v>
       </c>
       <c r="K12" s="4">
         <v>92.50176439451883</v>
@@ -5345,13 +5345,13 @@
         <v>0.5763688760806917</v>
       </c>
       <c r="H13" s="4">
-        <v>0.1825980500632818</v>
+        <v>0.1708738841672683</v>
       </c>
       <c r="I13" s="4">
-        <v>0.1683633863416875</v>
+        <v>0.1535357360681573</v>
       </c>
       <c r="J13" s="4">
-        <v>0.1918596182313367</v>
+        <v>0.1729770138210198</v>
       </c>
       <c r="K13" s="4">
         <v>97.37913897547494</v>
@@ -5395,13 +5395,13 @@
         <v>0.5763688760806917</v>
       </c>
       <c r="H14" s="4">
-        <v>0.246303009297761</v>
+        <v>0.2401193743269056</v>
       </c>
       <c r="I14" s="4">
-        <v>0.2273776305827702</v>
+        <v>0.2199873775666635</v>
       </c>
       <c r="J14" s="4">
-        <v>0.4416779432224178</v>
+        <v>0.4616897829840851</v>
       </c>
       <c r="K14" s="4">
         <v>87.91193710913753</v>
@@ -5445,13 +5445,13 @@
         <v>0.5763688760806917</v>
       </c>
       <c r="H15" s="4">
-        <v>0.1195925069684077</v>
+        <v>0.1107616601957439</v>
       </c>
       <c r="I15" s="4">
-        <v>0.1054378188977063</v>
+        <v>0.0954992404035741</v>
       </c>
       <c r="J15" s="4">
-        <v>0.1201306654782267</v>
+        <v>0.1064802948242592</v>
       </c>
       <c r="K15" s="4">
         <v>97.87498284616444</v>
@@ -5495,13 +5495,13 @@
         <v>0.5763688760806917</v>
       </c>
       <c r="H16" s="4">
-        <v>0.1706512182520463</v>
+        <v>0.1557555530748647</v>
       </c>
       <c r="I16" s="4">
-        <v>0.1515178995253006</v>
+        <v>0.1340621332474071</v>
       </c>
       <c r="J16" s="4">
-        <v>0.1702979141645274</v>
+        <v>0.1513420159072542</v>
       </c>
       <c r="K16" s="4">
         <v>98.82888313826874</v>
@@ -5545,13 +5545,13 @@
         <v>0.5763688760806917</v>
       </c>
       <c r="H17" s="4">
-        <v>0.2361258541394631</v>
+        <v>0.2264608589240886</v>
       </c>
       <c r="I17" s="4">
-        <v>0.1927341976959317</v>
+        <v>0.1806036739113432</v>
       </c>
       <c r="J17" s="4">
-        <v>0.3059888861468635</v>
+        <v>0.3232118697820403</v>
       </c>
       <c r="K17" s="4">
         <v>93.1867415554118</v>
@@ -5595,13 +5595,13 @@
         <v>0.5763688760806917</v>
       </c>
       <c r="H18" s="4">
-        <v>0.1768371273723198</v>
+        <v>0.1735199076559998</v>
       </c>
       <c r="I18" s="4">
-        <v>0.1630723834853231</v>
+        <v>0.1594546609498695</v>
       </c>
       <c r="J18" s="4">
-        <v>0.1799858771033051</v>
+        <v>0.1784211806100333</v>
       </c>
       <c r="K18" s="4">
         <v>96.16298104256124</v>
@@ -5645,13 +5645,13 @@
         <v>0.5763688760806917</v>
       </c>
       <c r="H19" s="4">
-        <v>0.1519153742868529</v>
+        <v>0.1461395456336421</v>
       </c>
       <c r="I19" s="4">
-        <v>0.1344825503394707</v>
+        <v>0.1271595888826005</v>
       </c>
       <c r="J19" s="4">
-        <v>0.1597716841239765</v>
+        <v>0.1570272476704784</v>
       </c>
       <c r="K19" s="4">
         <v>95.55063812268486</v>
@@ -5695,13 +5695,13 @@
         <v>0.5763688760806917</v>
       </c>
       <c r="H20" s="4">
-        <v>0.1322157128016992</v>
+        <v>0.1216927714799117</v>
       </c>
       <c r="I20" s="4">
-        <v>0.1131597729289562</v>
+        <v>0.1009539221814352</v>
       </c>
       <c r="J20" s="4">
-        <v>0.1373656956960403</v>
+        <v>0.1200380197348361</v>
       </c>
       <c r="K20" s="4">
         <v>99.59757101687941</v>
@@ -5745,13 +5745,13 @@
         <v>0.5788712011577424</v>
       </c>
       <c r="H21" s="4">
-        <v>0.1349684804848136</v>
+        <v>0.1182523907174312</v>
       </c>
       <c r="I21" s="4">
-        <v>0.1204863798305592</v>
+        <v>0.1031443464183097</v>
       </c>
       <c r="J21" s="4">
-        <v>0.137604076417054</v>
+        <v>0.117822007053355</v>
       </c>
       <c r="K21" s="4">
         <v>91.44068046900384</v>
@@ -5795,13 +5795,13 @@
         <v>0.5788712011577424</v>
       </c>
       <c r="H22" s="4">
-        <v>0.1424717044585462</v>
+        <v>0.1277010189696665</v>
       </c>
       <c r="I22" s="4">
-        <v>0.1277575815170843</v>
+        <v>0.1117782528441484</v>
       </c>
       <c r="J22" s="4">
-        <v>0.1414489677519044</v>
+        <v>0.1227564806218756</v>
       </c>
       <c r="K22" s="4">
         <v>91.18117290331443</v>
@@ -5845,13 +5845,13 @@
         <v>0.5763688760806917</v>
       </c>
       <c r="H23" s="4">
-        <v>0.1305250916553865</v>
+        <v>0.1157518564118939</v>
       </c>
       <c r="I23" s="4">
-        <v>0.1159481134847588</v>
+        <v>0.1002713865993335</v>
       </c>
       <c r="J23" s="4">
-        <v>0.1311817536967869</v>
+        <v>0.1144034777330842</v>
       </c>
       <c r="K23" s="4">
         <v>95.57612382128647</v>
@@ -6038,16 +6038,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.04509766402599594</v>
+        <v>-0.0660610145704652</v>
       </c>
       <c r="O3" s="5">
         <v>293</v>
       </c>
       <c r="P3" s="4">
-        <v>0.191379977891472</v>
+        <v>0.1904392591444908</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1947954898256147</v>
+        <v>0.1939647840891816</v>
       </c>
       <c r="R3" s="5">
         <v>293</v>
@@ -6097,16 +6097,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1394185223740971</v>
+        <v>-0.09287931697398211</v>
       </c>
       <c r="O4" s="5">
         <v>232</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1459198329633928</v>
+        <v>0.1375558223678635</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1011940718218358</v>
+        <v>0.09186684691059349</v>
       </c>
       <c r="R4" s="5">
         <v>228</v>
@@ -6156,16 +6156,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1916165400422406</v>
+        <v>-0.207068508909046</v>
       </c>
       <c r="O5" s="5">
         <v>154</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1943281295994118</v>
+        <v>0.193860865632574</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1943281295994118</v>
+        <v>0.193860865632574</v>
       </c>
       <c r="R5" s="5">
         <v>154</v>
@@ -6338,16 +6338,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4871476295408509</v>
+        <v>-0.4428498817163842</v>
       </c>
       <c r="O3" s="5">
         <v>271</v>
       </c>
       <c r="P3" s="4">
-        <v>0.185457038455609</v>
+        <v>0.1856785652039455</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1827060025060375</v>
+        <v>0.1811643872283607</v>
       </c>
       <c r="R3" s="5">
         <v>271</v>
@@ -6397,16 +6397,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2662156975952035</v>
+        <v>-0.1968566915264582</v>
       </c>
       <c r="O4" s="5">
         <v>231</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1322630431246965</v>
+        <v>0.1169004267599267</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.09056257893966028</v>
+        <v>0.07349691455953776</v>
       </c>
       <c r="R4" s="5">
         <v>227</v>
@@ -6456,16 +6456,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.5382972483673754</v>
+        <v>-0.5752612216724913</v>
       </c>
       <c r="O5" s="5">
         <v>153</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1144381552325891</v>
+        <v>0.111110049211879</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.114229465180107</v>
+        <v>0.1111212014292296</v>
       </c>
       <c r="R5" s="5">
         <v>153</v>
@@ -6638,16 +6638,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2626532384357471</v>
+        <v>0.3084742401456992</v>
       </c>
       <c r="O3" s="5">
         <v>287</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1728659889978673</v>
+        <v>0.1701962835832631</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1664594840548649</v>
+        <v>0.1614293864316224</v>
       </c>
       <c r="R3" s="5">
         <v>287</v>
@@ -6697,16 +6697,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.005244266402499206</v>
+        <v>0.05511176424712527</v>
       </c>
       <c r="O4" s="5">
         <v>232</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1305145838986274</v>
+        <v>0.1050472961496591</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.08637903314548651</v>
+        <v>0.05940607314391132</v>
       </c>
       <c r="R4" s="5">
         <v>228</v>
@@ -6756,16 +6756,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1004790515634449</v>
+        <v>0.1177805953916859</v>
       </c>
       <c r="O5" s="5">
         <v>154</v>
       </c>
       <c r="P5" s="4">
-        <v>0.05347790005554887</v>
+        <v>0.04976204777073222</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.05347790005554887</v>
+        <v>0.04976204777073222</v>
       </c>
       <c r="R5" s="5">
         <v>154</v>
@@ -6938,16 +6938,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.6964471507120458</v>
+        <v>0.7657173875400929</v>
       </c>
       <c r="O3" s="5">
         <v>306</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1661963738318826</v>
+        <v>0.1542861907509126</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1659617848818025</v>
+        <v>0.1537863063109338</v>
       </c>
       <c r="R3" s="5">
         <v>306</v>
@@ -6997,16 +6997,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>0.09332190511304479</v>
+        <v>0.1624585687914899</v>
       </c>
       <c r="O4" s="5">
         <v>231</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1389719619344004</v>
+        <v>0.105304993272381</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.0957310147496046</v>
+        <v>0.06025252833709244</v>
       </c>
       <c r="R4" s="5">
         <v>227</v>
@@ -7056,16 +7056,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4321987437689803</v>
+        <v>0.4399830838275278</v>
       </c>
       <c r="O5" s="5">
         <v>153</v>
       </c>
       <c r="P5" s="4">
-        <v>0.06626411792007679</v>
+        <v>0.06549730705421404</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.06626411792007679</v>
+        <v>0.06549730705421404</v>
       </c>
       <c r="R5" s="5">
         <v>153</v>
@@ -7238,16 +7238,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.5823196196068612</v>
+        <v>0.6361122915355679</v>
       </c>
       <c r="O3" s="5">
         <v>303</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1770103398802294</v>
+        <v>0.1713791462479735</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1772183131185924</v>
+        <v>0.1708026460135845</v>
       </c>
       <c r="R3" s="5">
         <v>303</v>
@@ -7297,16 +7297,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>0.08913460348938886</v>
+        <v>0.1642211623088081</v>
       </c>
       <c r="O4" s="5">
         <v>230</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1380690090288192</v>
+        <v>0.1028162806956927</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.09480116101348371</v>
+        <v>0.05710729800884073</v>
       </c>
       <c r="R4" s="5">
         <v>226</v>
@@ -7356,16 +7356,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4721145678160595</v>
+        <v>0.4905334106274353</v>
       </c>
       <c r="O5" s="5">
         <v>149</v>
       </c>
       <c r="P5" s="4">
-        <v>0.07981589772527935</v>
+        <v>0.07763036189023967</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.07716395305102233</v>
+        <v>0.07467251232361415</v>
       </c>
       <c r="R5" s="5">
         <v>149</v>
@@ -7538,16 +7538,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.6674455712728179</v>
+        <v>0.7186304677275643</v>
       </c>
       <c r="O3" s="5">
         <v>306</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1552214953599204</v>
+        <v>0.1503851654236863</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1551221075326654</v>
+        <v>0.1499196257899542</v>
       </c>
       <c r="R3" s="5">
         <v>306</v>
@@ -7597,16 +7597,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>0.06266496222840873</v>
+        <v>0.1304655768359111</v>
       </c>
       <c r="O4" s="5">
         <v>231</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1363698945924287</v>
+        <v>0.1027387175522906</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.0931559919053223</v>
+        <v>0.05729063443241673</v>
       </c>
       <c r="R4" s="5">
         <v>227</v>
@@ -7656,16 +7656,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3665682988823945</v>
+        <v>0.395451363582481</v>
       </c>
       <c r="O5" s="5">
         <v>151</v>
       </c>
       <c r="P5" s="4">
-        <v>0.07232712657493043</v>
+        <v>0.06608944757939993</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.07082605666272372</v>
+        <v>0.06427317169575826</v>
       </c>
       <c r="R5" s="5">
         <v>151</v>
@@ -9876,16 +9876,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.06518891021182366</v>
+        <v>0.1521063197472046</v>
       </c>
       <c r="O3" s="5">
         <v>271</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2414794305780882</v>
+        <v>0.2421293005024216</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2362093367003619</v>
+        <v>0.2273203699469612</v>
       </c>
       <c r="R3" s="5">
         <v>271</v>
@@ -9935,16 +9935,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2983983303771915</v>
+        <v>-0.2180172582355757</v>
       </c>
       <c r="O4" s="5">
         <v>229</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1400471417350625</v>
+        <v>0.1115114478008537</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.09682705381842611</v>
+        <v>0.06490283827296935</v>
       </c>
       <c r="R4" s="5">
         <v>225</v>
@@ -9994,16 +9994,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3934116322213624</v>
+        <v>-0.4360019814839688</v>
       </c>
       <c r="O5" s="5">
         <v>154</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1130621956767872</v>
+        <v>0.106479207941144</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1130621956767872</v>
+        <v>0.106479207941144</v>
       </c>
       <c r="R5" s="5">
         <v>154</v>
@@ -10176,16 +10176,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1561613302062876</v>
+        <v>-0.1205036695394597</v>
       </c>
       <c r="O3" s="5">
         <v>279</v>
       </c>
       <c r="P3" s="4">
-        <v>0.246034675249204</v>
+        <v>0.244748750962189</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2450856861865292</v>
+        <v>0.2420942612605463</v>
       </c>
       <c r="R3" s="5">
         <v>279</v>
@@ -10235,16 +10235,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1821133838197395</v>
+        <v>-0.1465950452361691</v>
       </c>
       <c r="O4" s="5">
         <v>211</v>
       </c>
       <c r="P4" s="4">
-        <v>0.159461458032523</v>
+        <v>0.1558432162647036</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1157150819621666</v>
+        <v>0.1088751472831033</v>
       </c>
       <c r="R4" s="5">
         <v>207</v>
@@ -10294,16 +10294,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2879505090378867</v>
+        <v>-0.3385874702590712</v>
       </c>
       <c r="O5" s="5">
         <v>152</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1737474565787117</v>
+        <v>0.1698684000215104</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1707147312694679</v>
+        <v>0.1661183586888668</v>
       </c>
       <c r="R5" s="5">
         <v>152</v>
@@ -10476,16 +10476,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5552791065275079</v>
+        <v>-0.4740597714843489</v>
       </c>
       <c r="O3" s="5">
         <v>101</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2893908034884709</v>
+        <v>0.294885633536998</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3315576615430237</v>
+        <v>0.326310888212599</v>
       </c>
       <c r="R3" s="5">
         <v>101</v>
@@ -10535,16 +10535,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>0.04079672490408567</v>
+        <v>0.1273249700561458</v>
       </c>
       <c r="O4" s="5">
         <v>224</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2019003699061209</v>
+        <v>0.178465115167025</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1582719246096924</v>
+        <v>0.1311985220170442</v>
       </c>
       <c r="R4" s="5">
         <v>220</v>
@@ -10594,16 +10594,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.8199264452808004</v>
+        <v>-0.8964201855469156</v>
       </c>
       <c r="O5" s="5">
         <v>154</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1523299760084152</v>
+        <v>0.1383973322088042</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1523299760084152</v>
+        <v>0.1383973322088042</v>
       </c>
       <c r="R5" s="5">
         <v>154</v>
@@ -10776,16 +10776,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2107684384597833</v>
+        <v>-0.1908948707266376</v>
       </c>
       <c r="O3" s="5">
         <v>305</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1445831666221289</v>
+        <v>0.1430432168845531</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1451307177474108</v>
+        <v>0.1434503515018302</v>
       </c>
       <c r="R3" s="5">
         <v>305</v>
@@ -10835,16 +10835,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.05486562103821628</v>
+        <v>0.01482281778416006</v>
       </c>
       <c r="O4" s="5">
         <v>231</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1400700520416136</v>
+        <v>0.110372806961453</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.09733389359355182</v>
+        <v>0.06588535892920556</v>
       </c>
       <c r="R4" s="5">
         <v>227</v>
@@ -10894,16 +10894,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2886066455250434</v>
+        <v>-0.3874388994085365</v>
       </c>
       <c r="O5" s="5">
         <v>153</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2012543914915975</v>
+        <v>0.186123469812312</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2012543914915975</v>
+        <v>0.186123469812312</v>
       </c>
       <c r="R5" s="5">
         <v>153</v>
@@ -11076,16 +11076,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.426705432864507</v>
+        <v>0.6250436099938668</v>
       </c>
       <c r="O3" s="5">
         <v>153</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6270532656210741</v>
+        <v>0.6959721070285031</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3848309962227004</v>
+        <v>0.3451216415104041</v>
       </c>
       <c r="R3" s="5">
         <v>153</v>
@@ -11135,16 +11135,16 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.03584356198858929</v>
+        <v>0.04482621026775302</v>
       </c>
       <c r="O4" s="5">
         <v>223</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2882418294013097</v>
+        <v>0.2696619844244866</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1482361444402633</v>
+        <v>0.1249546745214982</v>
       </c>
       <c r="R4" s="5">
         <v>219</v>
@@ -11194,16 +11194,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4215640995115584</v>
+        <v>-0.3397869034244394</v>
       </c>
       <c r="O5" s="5">
         <v>137</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3734327072429083</v>
+        <v>0.3670701294232942</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1642828293476696</v>
+        <v>0.1476886292722193</v>
       </c>
       <c r="R5" s="5">
         <v>137</v>
